--- a/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
@@ -178,7 +178,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -206,7 +206,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -234,7 +234,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -262,7 +262,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8A9A2B"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -290,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A9A9A"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -318,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -346,7 +346,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6E4B2A"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -361,6 +361,34 @@
           <val>
             <numRef>
               <f>'Chart'!$H$2:$H$141</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9A9A9A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$141</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$141</f>
             </numRef>
           </val>
         </ser>
@@ -452,7 +480,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -839,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -853,37 +881,42 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Bioenergy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Oil</t>
+          <t>Other (oil, fuel cells, pumped storage, other)</t>
         </is>
       </c>
     </row>
@@ -892,25 +925,28 @@
         <v>42005</v>
       </c>
       <c r="B2" t="n">
+        <v>200.622167404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11483.952865645</v>
+      </c>
+      <c r="D2" t="n">
+        <v>157.511584753</v>
+      </c>
+      <c r="E2" t="n">
+        <v>90.76126542700001</v>
+      </c>
+      <c r="F2" t="n">
         <v>18745.230464441</v>
       </c>
-      <c r="C2" t="n">
+      <c r="G2" t="n">
         <v>13577.81680492</v>
       </c>
-      <c r="D2" t="n">
-        <v>11483.952865645</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>931.535332313</v>
       </c>
-      <c r="F2" t="n">
-        <v>700.775126957</v>
-      </c>
-      <c r="G2" t="n">
-        <v>90.76126542700001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>685.169926155</v>
+      <c r="I2" t="n">
+        <v>1160.282550808</v>
       </c>
     </row>
     <row r="3">
@@ -918,25 +954,28 @@
         <v>42036</v>
       </c>
       <c r="B3" t="n">
+        <v>182.436631318</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9432.042749091001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>136.770823455</v>
+      </c>
+      <c r="E3" t="n">
+        <v>98.063715433</v>
+      </c>
+      <c r="F3" t="n">
         <v>16495.532688869</v>
       </c>
-      <c r="C3" t="n">
+      <c r="G3" t="n">
         <v>11550.157975414</v>
       </c>
-      <c r="D3" t="n">
-        <v>9432.042749091001</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>774.4578696120001</v>
       </c>
-      <c r="F3" t="n">
-        <v>623.531104397</v>
-      </c>
-      <c r="G3" t="n">
-        <v>98.063715433</v>
-      </c>
-      <c r="H3" t="n">
-        <v>714.4835828080001</v>
+      <c r="I3" t="n">
+        <v>1142.278665481</v>
       </c>
     </row>
     <row r="4">
@@ -944,25 +983,28 @@
         <v>42064</v>
       </c>
       <c r="B4" t="n">
+        <v>194.704477407</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10271.186864045</v>
+      </c>
+      <c r="D4" t="n">
+        <v>130.759594207</v>
+      </c>
+      <c r="E4" t="n">
+        <v>155.346338069</v>
+      </c>
+      <c r="F4" t="n">
         <v>17167.976051337</v>
       </c>
-      <c r="C4" t="n">
+      <c r="G4" t="n">
         <v>12445.388334258</v>
       </c>
-      <c r="D4" t="n">
-        <v>10271.186864045</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>886.4482594010001</v>
       </c>
-      <c r="F4" t="n">
-        <v>651.870569788</v>
-      </c>
-      <c r="G4" t="n">
-        <v>155.346338069</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1554.018443037</v>
+      <c r="I4" t="n">
+        <v>2013.797114376</v>
       </c>
     </row>
     <row r="5">
@@ -970,25 +1012,28 @@
         <v>42095</v>
       </c>
       <c r="B5" t="n">
+        <v>230.794572895</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8576.291489316</v>
+      </c>
+      <c r="D5" t="n">
+        <v>106.842246334</v>
+      </c>
+      <c r="E5" t="n">
+        <v>125.115822199</v>
+      </c>
+      <c r="F5" t="n">
         <v>15763.324576332</v>
       </c>
-      <c r="C5" t="n">
+      <c r="G5" t="n">
         <v>12412.716096119</v>
       </c>
-      <c r="D5" t="n">
-        <v>8576.291489316</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>876.2727888690001</v>
       </c>
-      <c r="F5" t="n">
-        <v>531.77701366</v>
-      </c>
-      <c r="G5" t="n">
-        <v>125.115822199</v>
-      </c>
-      <c r="H5" t="n">
-        <v>841.80001325</v>
+      <c r="I5" t="n">
+        <v>1161.968857881</v>
       </c>
     </row>
     <row r="6">
@@ -996,25 +1041,28 @@
         <v>42125</v>
       </c>
       <c r="B6" t="n">
+        <v>281.098686762</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8104.650425011</v>
+      </c>
+      <c r="D6" t="n">
+        <v>96.67265754099999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>177.396524697</v>
+      </c>
+      <c r="F6" t="n">
         <v>16150.73342638</v>
       </c>
-      <c r="C6" t="n">
+      <c r="G6" t="n">
         <v>12020.87544349</v>
       </c>
-      <c r="D6" t="n">
-        <v>8104.650425011</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>856.23832521</v>
       </c>
-      <c r="F6" t="n">
-        <v>550.3745169</v>
-      </c>
-      <c r="G6" t="n">
-        <v>177.396524697</v>
-      </c>
-      <c r="H6" t="n">
-        <v>468.693012803</v>
+      <c r="I6" t="n">
+        <v>772.1574828510001</v>
       </c>
     </row>
     <row r="7">
@@ -1022,25 +1070,28 @@
         <v>42156</v>
       </c>
       <c r="B7" t="n">
+        <v>217.078513722</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8268.192518148</v>
+      </c>
+      <c r="D7" t="n">
+        <v>53.959587708</v>
+      </c>
+      <c r="E7" t="n">
+        <v>137.680087017</v>
+      </c>
+      <c r="F7" t="n">
         <v>16191.930095926</v>
       </c>
-      <c r="C7" t="n">
+      <c r="G7" t="n">
         <v>12898.827552501</v>
       </c>
-      <c r="D7" t="n">
-        <v>8268.192518148</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>939.902288496</v>
       </c>
-      <c r="F7" t="n">
-        <v>409.964952216</v>
-      </c>
-      <c r="G7" t="n">
-        <v>137.680087017</v>
-      </c>
-      <c r="H7" t="n">
-        <v>280.233433015</v>
+      <c r="I7" t="n">
+        <v>544.8984864609999</v>
       </c>
     </row>
     <row r="8">
@@ -1048,25 +1099,28 @@
         <v>42186</v>
       </c>
       <c r="B8" t="n">
+        <v>204.310679905</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7579.926646848</v>
+      </c>
+      <c r="D8" t="n">
+        <v>95.99440517699999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>137.720492354</v>
+      </c>
+      <c r="F8" t="n">
         <v>17870.725244622</v>
       </c>
-      <c r="C8" t="n">
+      <c r="G8" t="n">
         <v>15087.95110634</v>
       </c>
-      <c r="D8" t="n">
-        <v>7579.926646848</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>945.649633163</v>
       </c>
-      <c r="F8" t="n">
-        <v>787.772663102</v>
-      </c>
-      <c r="G8" t="n">
-        <v>137.720492354</v>
-      </c>
-      <c r="H8" t="n">
-        <v>229.151088483</v>
+      <c r="I8" t="n">
+        <v>847.612440797</v>
       </c>
     </row>
     <row r="9">
@@ -1074,25 +1128,28 @@
         <v>42217</v>
       </c>
       <c r="B9" t="n">
+        <v>155.935238504</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9620.729190053</v>
+      </c>
+      <c r="D9" t="n">
+        <v>65.890475845</v>
+      </c>
+      <c r="E9" t="n">
+        <v>151.266880125</v>
+      </c>
+      <c r="F9" t="n">
         <v>18417.133636368</v>
       </c>
-      <c r="C9" t="n">
+      <c r="G9" t="n">
         <v>12640.120034969</v>
       </c>
-      <c r="D9" t="n">
-        <v>9620.729190053</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>988.355241847</v>
       </c>
-      <c r="F9" t="n">
-        <v>726.535254409</v>
-      </c>
-      <c r="G9" t="n">
-        <v>151.266880125</v>
-      </c>
-      <c r="H9" t="n">
-        <v>409.581513956</v>
+      <c r="I9" t="n">
+        <v>1044.869442188</v>
       </c>
     </row>
     <row r="10">
@@ -1100,25 +1157,28 @@
         <v>42248</v>
       </c>
       <c r="B10" t="n">
+        <v>136.032565725</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8328.365301057</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69.785685958</v>
+      </c>
+      <c r="E10" t="n">
+        <v>153.481573747</v>
+      </c>
+      <c r="F10" t="n">
         <v>15739.148049892</v>
       </c>
-      <c r="C10" t="n">
+      <c r="G10" t="n">
         <v>12178.226249422</v>
       </c>
-      <c r="D10" t="n">
-        <v>8328.365301057</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>975.554622416</v>
       </c>
-      <c r="F10" t="n">
-        <v>575.867476831</v>
-      </c>
-      <c r="G10" t="n">
-        <v>153.481573747</v>
-      </c>
-      <c r="H10" t="n">
-        <v>394.478336031</v>
+      <c r="I10" t="n">
+        <v>894.9286443110001</v>
       </c>
     </row>
     <row r="11">
@@ -1126,25 +1186,28 @@
         <v>42278</v>
       </c>
       <c r="B11" t="n">
+        <v>129.661317471</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8337.502655046001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>128.942985905</v>
+      </c>
+      <c r="E11" t="n">
+        <v>152.964146289</v>
+      </c>
+      <c r="F11" t="n">
         <v>14891.293521805</v>
       </c>
-      <c r="C11" t="n">
+      <c r="G11" t="n">
         <v>13703.511673446</v>
       </c>
-      <c r="D11" t="n">
-        <v>8337.502655046001</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>1004.055642536</v>
       </c>
-      <c r="F11" t="n">
-        <v>535.989557718</v>
-      </c>
-      <c r="G11" t="n">
-        <v>152.964146289</v>
-      </c>
-      <c r="H11" t="n">
-        <v>561.15019692</v>
+      <c r="I11" t="n">
+        <v>977.2413691769999</v>
       </c>
     </row>
     <row r="12">
@@ -1152,25 +1215,28 @@
         <v>42309</v>
       </c>
       <c r="B12" t="n">
+        <v>91.77658068699999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7341.359438435</v>
+      </c>
+      <c r="D12" t="n">
+        <v>121.975931274</v>
+      </c>
+      <c r="E12" t="n">
+        <v>66.46671881</v>
+      </c>
+      <c r="F12" t="n">
         <v>15476.639693186</v>
       </c>
-      <c r="C12" t="n">
+      <c r="G12" t="n">
         <v>14140.946580212</v>
       </c>
-      <c r="D12" t="n">
-        <v>7341.359438435</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>928.449047025</v>
       </c>
-      <c r="F12" t="n">
-        <v>450.594635415</v>
-      </c>
-      <c r="G12" t="n">
-        <v>66.46671881</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1597.5182099</v>
+      <c r="I12" t="n">
+        <v>1969.780120749</v>
       </c>
     </row>
     <row r="13">
@@ -1178,25 +1244,28 @@
         <v>42339</v>
       </c>
       <c r="B13" t="n">
+        <v>82.51433347699999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9081.64436416</v>
+      </c>
+      <c r="D13" t="n">
+        <v>170.809395844</v>
+      </c>
+      <c r="E13" t="n">
+        <v>86.958144245</v>
+      </c>
+      <c r="F13" t="n">
         <v>18160.061215654</v>
       </c>
-      <c r="C13" t="n">
+      <c r="G13" t="n">
         <v>14510.834508733</v>
       </c>
-      <c r="D13" t="n">
-        <v>9081.64436416</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>987.379984544</v>
       </c>
-      <c r="F13" t="n">
-        <v>538.8816108579999</v>
-      </c>
-      <c r="G13" t="n">
-        <v>86.958144245</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1671.064056725</v>
+      <c r="I13" t="n">
+        <v>2097.524813893</v>
       </c>
     </row>
     <row r="14">
@@ -1204,25 +1273,28 @@
         <v>42370</v>
       </c>
       <c r="B14" t="n">
+        <v>91.854299604</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10849.143270086</v>
+      </c>
+      <c r="D14" t="n">
+        <v>214.532639997</v>
+      </c>
+      <c r="E14" t="n">
+        <v>96.878184441</v>
+      </c>
+      <c r="F14" t="n">
         <v>17992.1479239</v>
       </c>
-      <c r="C14" t="n">
+      <c r="G14" t="n">
         <v>14725.389881289</v>
       </c>
-      <c r="D14" t="n">
-        <v>10849.143270086</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>940.08564629</v>
       </c>
-      <c r="F14" t="n">
-        <v>634.5772563630001</v>
-      </c>
-      <c r="G14" t="n">
-        <v>96.878184441</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1707.680250738</v>
+      <c r="I14" t="n">
+        <v>2180.694419245</v>
       </c>
     </row>
     <row r="15">
@@ -1230,25 +1302,28 @@
         <v>42401</v>
       </c>
       <c r="B15" t="n">
+        <v>85.312992662</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9102.398514697001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>213.155627677</v>
+      </c>
+      <c r="E15" t="n">
+        <v>135.112464301</v>
+      </c>
+      <c r="F15" t="n">
         <v>15884.445964572</v>
       </c>
-      <c r="C15" t="n">
+      <c r="G15" t="n">
         <v>13507.743872993</v>
       </c>
-      <c r="D15" t="n">
-        <v>9102.398514697001</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>871.7191068029999</v>
       </c>
-      <c r="F15" t="n">
-        <v>604.173385087</v>
-      </c>
-      <c r="G15" t="n">
-        <v>135.112464301</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1539.098392899</v>
+      <c r="I15" t="n">
+        <v>1987.105887759</v>
       </c>
     </row>
     <row r="16">
@@ -1256,25 +1331,28 @@
         <v>42430</v>
       </c>
       <c r="B16" t="n">
+        <v>150.15270844</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9348.366671987</v>
+      </c>
+      <c r="D16" t="n">
+        <v>143.910001085</v>
+      </c>
+      <c r="E16" t="n">
+        <v>179.113679562</v>
+      </c>
+      <c r="F16" t="n">
         <v>16396.455332432</v>
       </c>
-      <c r="C16" t="n">
+      <c r="G16" t="n">
         <v>13920.65451915</v>
       </c>
-      <c r="D16" t="n">
-        <v>9348.366671987</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="H16" t="n">
         <v>909.16537658</v>
       </c>
-      <c r="F16" t="n">
-        <v>536.042386714</v>
-      </c>
-      <c r="G16" t="n">
-        <v>179.113679562</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1721.17895521</v>
+      <c r="I16" t="n">
+        <v>2109.473667159</v>
       </c>
     </row>
     <row r="17">
@@ -1282,25 +1360,28 @@
         <v>42461</v>
       </c>
       <c r="B17" t="n">
+        <v>223.648267206</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6524.20536933</v>
+      </c>
+      <c r="D17" t="n">
+        <v>132.906224898</v>
+      </c>
+      <c r="E17" t="n">
+        <v>172.413927636</v>
+      </c>
+      <c r="F17" t="n">
         <v>14715.295584599</v>
       </c>
-      <c r="C17" t="n">
+      <c r="G17" t="n">
         <v>14633.224254128</v>
       </c>
-      <c r="D17" t="n">
-        <v>6524.20536933</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="H17" t="n">
         <v>959.8436960849999</v>
       </c>
-      <c r="F17" t="n">
-        <v>595.413800616</v>
-      </c>
-      <c r="G17" t="n">
-        <v>172.413927636</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1204.34759368</v>
+      <c r="I17" t="n">
+        <v>1593.694631424</v>
       </c>
     </row>
     <row r="18">
@@ -1308,25 +1389,28 @@
         <v>42491</v>
       </c>
       <c r="B18" t="n">
+        <v>343.889344623</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7039.221343272</v>
+      </c>
+      <c r="D18" t="n">
+        <v>132.055757419</v>
+      </c>
+      <c r="E18" t="n">
+        <v>206.285703009</v>
+      </c>
+      <c r="F18" t="n">
         <v>16381.405668464</v>
       </c>
-      <c r="C18" t="n">
+      <c r="G18" t="n">
         <v>13340.89070342</v>
       </c>
-      <c r="D18" t="n">
-        <v>7039.221343272</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="H18" t="n">
         <v>906.1459944860001</v>
       </c>
-      <c r="F18" t="n">
-        <v>760.729422234</v>
-      </c>
-      <c r="G18" t="n">
-        <v>206.285703009</v>
-      </c>
-      <c r="H18" t="n">
-        <v>902.834318348</v>
+      <c r="I18" t="n">
+        <v>1333.211910642</v>
       </c>
     </row>
     <row r="19">
@@ -1334,25 +1418,28 @@
         <v>42522</v>
       </c>
       <c r="B19" t="n">
+        <v>286.607402768</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8267.14815796</v>
+      </c>
+      <c r="D19" t="n">
+        <v>67.010973204</v>
+      </c>
+      <c r="E19" t="n">
+        <v>167.153234749</v>
+      </c>
+      <c r="F19" t="n">
         <v>17043.936371234</v>
       </c>
-      <c r="C19" t="n">
+      <c r="G19" t="n">
         <v>12348.853636392</v>
       </c>
-      <c r="D19" t="n">
-        <v>8267.14815796</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="H19" t="n">
         <v>802.867872263</v>
       </c>
-      <c r="F19" t="n">
-        <v>579.6176059769999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>167.153234749</v>
-      </c>
-      <c r="H19" t="n">
-        <v>766.8909392210001</v>
+      <c r="I19" t="n">
+        <v>1141.296967411</v>
       </c>
     </row>
     <row r="20">
@@ -1360,25 +1447,28 @@
         <v>42552</v>
       </c>
       <c r="B20" t="n">
+        <v>600.145450331</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9618.464169715</v>
+      </c>
+      <c r="D20" t="n">
+        <v>84.182540186</v>
+      </c>
+      <c r="E20" t="n">
+        <v>165.979979927</v>
+      </c>
+      <c r="F20" t="n">
         <v>18397.661399138</v>
       </c>
-      <c r="C20" t="n">
+      <c r="G20" t="n">
         <v>12911.834818759</v>
       </c>
-      <c r="D20" t="n">
-        <v>9618.464169715</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="H20" t="n">
         <v>930.7129124309999</v>
       </c>
-      <c r="F20" t="n">
-        <v>980.729978777</v>
-      </c>
-      <c r="G20" t="n">
-        <v>165.979979927</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1153.602600208</v>
+      <c r="I20" t="n">
+        <v>1633.186701157</v>
       </c>
     </row>
     <row r="21">
@@ -1386,25 +1476,28 @@
         <v>42583</v>
       </c>
       <c r="B21" t="n">
+        <v>276.676801375</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10205.71905117</v>
+      </c>
+      <c r="D21" t="n">
+        <v>74.75392412900001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>197.279627009</v>
+      </c>
+      <c r="F21" t="n">
         <v>19115.159815078</v>
       </c>
-      <c r="C21" t="n">
+      <c r="G21" t="n">
         <v>13935.366970869</v>
       </c>
-      <c r="D21" t="n">
-        <v>10205.71905117</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
         <v>1029.744326203</v>
       </c>
-      <c r="F21" t="n">
-        <v>764.176094613</v>
-      </c>
-      <c r="G21" t="n">
-        <v>197.279627009</v>
-      </c>
-      <c r="H21" t="n">
-        <v>791.635948895</v>
+      <c r="I21" t="n">
+        <v>1450.987369606</v>
       </c>
     </row>
     <row r="22">
@@ -1412,25 +1505,28 @@
         <v>42614</v>
       </c>
       <c r="B22" t="n">
+        <v>199.282179418</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8658.394101192</v>
+      </c>
+      <c r="D22" t="n">
+        <v>69.961486928</v>
+      </c>
+      <c r="E22" t="n">
+        <v>133.733569853</v>
+      </c>
+      <c r="F22" t="n">
         <v>16283.337819256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="G22" t="n">
         <v>12063.350283467</v>
       </c>
-      <c r="D22" t="n">
-        <v>8658.394101192</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="H22" t="n">
         <v>970.041031843</v>
       </c>
-      <c r="F22" t="n">
-        <v>669.254766478</v>
-      </c>
-      <c r="G22" t="n">
-        <v>133.733569853</v>
-      </c>
-      <c r="H22" t="n">
-        <v>478.426023434</v>
+      <c r="I22" t="n">
+        <v>1036.203064308</v>
       </c>
     </row>
     <row r="23">
@@ -1438,25 +1534,28 @@
         <v>42644</v>
       </c>
       <c r="B23" t="n">
+        <v>173.499873925</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9882.642229356001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>126.141429918</v>
+      </c>
+      <c r="E23" t="n">
+        <v>118.26735127</v>
+      </c>
+      <c r="F23" t="n">
         <v>16373.668042937</v>
       </c>
-      <c r="C23" t="n">
+      <c r="G23" t="n">
         <v>11091.615911636</v>
       </c>
-      <c r="D23" t="n">
-        <v>9882.642229356001</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
         <v>960.0799458419999</v>
       </c>
-      <c r="F23" t="n">
-        <v>594.918125704</v>
-      </c>
-      <c r="G23" t="n">
-        <v>118.26735127</v>
-      </c>
-      <c r="H23" t="n">
-        <v>885.892387071</v>
+      <c r="I23" t="n">
+        <v>1406.309005228</v>
       </c>
     </row>
     <row r="24">
@@ -1464,25 +1563,28 @@
         <v>42675</v>
       </c>
       <c r="B24" t="n">
+        <v>161.029832242</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11732.892739054</v>
+      </c>
+      <c r="D24" t="n">
+        <v>174.667630742</v>
+      </c>
+      <c r="E24" t="n">
+        <v>121.479896618</v>
+      </c>
+      <c r="F24" t="n">
         <v>17610.806624008</v>
       </c>
-      <c r="C24" t="n">
+      <c r="G24" t="n">
         <v>9809.296273909</v>
       </c>
-      <c r="D24" t="n">
-        <v>11732.892739054</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="H24" t="n">
         <v>967.0413143530001</v>
       </c>
-      <c r="F24" t="n">
-        <v>610.455807689</v>
-      </c>
-      <c r="G24" t="n">
-        <v>121.479896618</v>
-      </c>
-      <c r="H24" t="n">
-        <v>792.607572363</v>
+      <c r="I24" t="n">
+        <v>1273.252495043</v>
       </c>
     </row>
     <row r="25">
@@ -1490,25 +1592,28 @@
         <v>42705</v>
       </c>
       <c r="B25" t="n">
+        <v>164.80577839</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10585.722717852</v>
+      </c>
+      <c r="D25" t="n">
+        <v>240.601135581</v>
+      </c>
+      <c r="E25" t="n">
+        <v>113.254303184</v>
+      </c>
+      <c r="F25" t="n">
         <v>20415.969572116</v>
       </c>
-      <c r="C25" t="n">
+      <c r="G25" t="n">
         <v>12021.840099126</v>
       </c>
-      <c r="D25" t="n">
-        <v>10585.722717852</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="H25" t="n">
         <v>953.4994260780001</v>
       </c>
-      <c r="F25" t="n">
-        <v>718.2868203089999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>113.254303184</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1335.474581724</v>
+      <c r="I25" t="n">
+        <v>1913.781267032</v>
       </c>
     </row>
     <row r="26">
@@ -1516,25 +1621,28 @@
         <v>42736</v>
       </c>
       <c r="B26" t="n">
+        <v>169.406816667</v>
+      </c>
+      <c r="C26" t="n">
+        <v>10229.14847569</v>
+      </c>
+      <c r="D26" t="n">
+        <v>258.097790542</v>
+      </c>
+      <c r="E26" t="n">
+        <v>143.233068532</v>
+      </c>
+      <c r="F26" t="n">
         <v>20513.945426445</v>
       </c>
-      <c r="C26" t="n">
+      <c r="G26" t="n">
         <v>12477.303431448</v>
       </c>
-      <c r="D26" t="n">
-        <v>10229.14847569</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
         <v>1030.979976261</v>
       </c>
-      <c r="F26" t="n">
-        <v>792.505309335</v>
-      </c>
-      <c r="G26" t="n">
-        <v>143.233068532</v>
-      </c>
-      <c r="H26" t="n">
-        <v>985.2123003090001</v>
+      <c r="I26" t="n">
+        <v>1582.283195657</v>
       </c>
     </row>
     <row r="27">
@@ -1542,25 +1650,28 @@
         <v>42767</v>
       </c>
       <c r="B27" t="n">
+        <v>154.869418113</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9594.393549625</v>
+      </c>
+      <c r="D27" t="n">
+        <v>255.62502233</v>
+      </c>
+      <c r="E27" t="n">
+        <v>180.625526686</v>
+      </c>
+      <c r="F27" t="n">
         <v>18278.722698888</v>
       </c>
-      <c r="C27" t="n">
+      <c r="G27" t="n">
         <v>11779.580374365</v>
       </c>
-      <c r="D27" t="n">
-        <v>9594.393549625</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="H27" t="n">
         <v>884.1258445840001</v>
       </c>
-      <c r="F27" t="n">
-        <v>761.8112909280001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>180.625526686</v>
-      </c>
-      <c r="H27" t="n">
-        <v>917.926346384</v>
+      <c r="I27" t="n">
+        <v>1448.027856003</v>
       </c>
     </row>
     <row r="28">
@@ -1568,25 +1679,28 @@
         <v>42795</v>
       </c>
       <c r="B28" t="n">
+        <v>171.745902496</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10047.259170997</v>
+      </c>
+      <c r="D28" t="n">
+        <v>166.028298567</v>
+      </c>
+      <c r="E28" t="n">
+        <v>225.523010431</v>
+      </c>
+      <c r="F28" t="n">
         <v>19190.661059405</v>
       </c>
-      <c r="C28" t="n">
+      <c r="G28" t="n">
         <v>12546.188156627</v>
       </c>
-      <c r="D28" t="n">
-        <v>10047.259170997</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="H28" t="n">
         <v>947.229610372</v>
       </c>
-      <c r="F28" t="n">
-        <v>665.458705906</v>
-      </c>
-      <c r="G28" t="n">
-        <v>225.523010431</v>
-      </c>
-      <c r="H28" t="n">
-        <v>266.596402089</v>
+      <c r="I28" t="n">
+        <v>895.435940677</v>
       </c>
     </row>
     <row r="29">
@@ -1594,25 +1708,28 @@
         <v>42826</v>
       </c>
       <c r="B29" t="n">
+        <v>194.960184408</v>
+      </c>
+      <c r="C29" t="n">
+        <v>7521.410026309</v>
+      </c>
+      <c r="D29" t="n">
+        <v>194.853877374</v>
+      </c>
+      <c r="E29" t="n">
+        <v>241.968108237</v>
+      </c>
+      <c r="F29" t="n">
         <v>16824.082277283</v>
       </c>
-      <c r="C29" t="n">
+      <c r="G29" t="n">
         <v>12672.353110448</v>
       </c>
-      <c r="D29" t="n">
-        <v>7521.410026309</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="H29" t="n">
         <v>878.7953078979999</v>
       </c>
-      <c r="F29" t="n">
-        <v>703.625385023</v>
-      </c>
-      <c r="G29" t="n">
-        <v>241.968108237</v>
-      </c>
-      <c r="H29" t="n">
-        <v>236.882840181</v>
+      <c r="I29" t="n">
+        <v>871.7113169290001</v>
       </c>
     </row>
     <row r="30">
@@ -1620,25 +1737,28 @@
         <v>42856</v>
       </c>
       <c r="B30" t="n">
+        <v>234.081271041</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7284.122617155</v>
+      </c>
+      <c r="D30" t="n">
+        <v>144.961112999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>269.437893348</v>
+      </c>
+      <c r="F30" t="n">
         <v>17377.863040214</v>
       </c>
-      <c r="C30" t="n">
+      <c r="G30" t="n">
         <v>13017.14576909</v>
       </c>
-      <c r="D30" t="n">
-        <v>7284.122617155</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="H30" t="n">
         <v>1008.093245394</v>
       </c>
-      <c r="F30" t="n">
-        <v>745.820290701</v>
-      </c>
-      <c r="G30" t="n">
-        <v>269.437893348</v>
-      </c>
-      <c r="H30" t="n">
-        <v>214.600032837</v>
+      <c r="I30" t="n">
+        <v>853.513350169</v>
       </c>
     </row>
     <row r="31">
@@ -1646,25 +1766,28 @@
         <v>42887</v>
       </c>
       <c r="B31" t="n">
+        <v>200.716631855</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9834.567036148999</v>
+      </c>
+      <c r="D31" t="n">
+        <v>83.200117177</v>
+      </c>
+      <c r="E31" t="n">
+        <v>249.895685162</v>
+      </c>
+      <c r="F31" t="n">
         <v>16971.543290745</v>
       </c>
-      <c r="C31" t="n">
+      <c r="G31" t="n">
         <v>11886.457193973</v>
       </c>
-      <c r="D31" t="n">
-        <v>9834.567036148999</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="H31" t="n">
         <v>996.268611982</v>
       </c>
-      <c r="F31" t="n">
-        <v>643.6090214559999</v>
-      </c>
-      <c r="G31" t="n">
-        <v>249.895685162</v>
-      </c>
-      <c r="H31" t="n">
-        <v>302.735899877</v>
+      <c r="I31" t="n">
+        <v>908.0179026899999</v>
       </c>
     </row>
     <row r="32">
@@ -1672,25 +1795,28 @@
         <v>42917</v>
       </c>
       <c r="B32" t="n">
+        <v>323.666987004</v>
+      </c>
+      <c r="C32" t="n">
+        <v>11651.691507144</v>
+      </c>
+      <c r="D32" t="n">
+        <v>127.216672159</v>
+      </c>
+      <c r="E32" t="n">
+        <v>187.602005201</v>
+      </c>
+      <c r="F32" t="n">
         <v>20972.152770038</v>
       </c>
-      <c r="C32" t="n">
+      <c r="G32" t="n">
         <v>11624.670885076</v>
       </c>
-      <c r="D32" t="n">
-        <v>11651.691507144</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="H32" t="n">
         <v>1059.156667461</v>
       </c>
-      <c r="F32" t="n">
-        <v>761.681941486</v>
-      </c>
-      <c r="G32" t="n">
-        <v>187.602005201</v>
-      </c>
-      <c r="H32" t="n">
-        <v>565.5785516559999</v>
+      <c r="I32" t="n">
+        <v>1091.323379891</v>
       </c>
     </row>
     <row r="33">
@@ -1698,25 +1824,28 @@
         <v>42948</v>
       </c>
       <c r="B33" t="n">
+        <v>526.194100993</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10159.217009182</v>
+      </c>
+      <c r="D33" t="n">
+        <v>103.793780779</v>
+      </c>
+      <c r="E33" t="n">
+        <v>219.009739278</v>
+      </c>
+      <c r="F33" t="n">
         <v>21638.971585911</v>
       </c>
-      <c r="C33" t="n">
+      <c r="G33" t="n">
         <v>11323.833128007</v>
       </c>
-      <c r="D33" t="n">
-        <v>10159.217009182</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="H33" t="n">
         <v>1120.340758135</v>
       </c>
-      <c r="F33" t="n">
-        <v>1064.197519219</v>
-      </c>
-      <c r="G33" t="n">
-        <v>219.009739278</v>
-      </c>
-      <c r="H33" t="n">
-        <v>366.967498374</v>
+      <c r="I33" t="n">
+        <v>1146.880264888</v>
       </c>
     </row>
     <row r="34">
@@ -1724,25 +1853,28 @@
         <v>42979</v>
       </c>
       <c r="B34" t="n">
+        <v>250.054462076</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7430.081832478</v>
+      </c>
+      <c r="D34" t="n">
+        <v>118.055183707</v>
+      </c>
+      <c r="E34" t="n">
+        <v>220.50231503</v>
+      </c>
+      <c r="F34" t="n">
         <v>19699.703698447</v>
       </c>
-      <c r="C34" t="n">
+      <c r="G34" t="n">
         <v>11729.511706788</v>
       </c>
-      <c r="D34" t="n">
-        <v>7430.081832478</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
         <v>1094.936757248</v>
       </c>
-      <c r="F34" t="n">
-        <v>786.62460487</v>
-      </c>
-      <c r="G34" t="n">
-        <v>220.50231503</v>
-      </c>
-      <c r="H34" t="n">
-        <v>239.50080639</v>
+      <c r="I34" t="n">
+        <v>987.1177365300001</v>
       </c>
     </row>
     <row r="35">
@@ -1750,25 +1882,28 @@
         <v>43009</v>
       </c>
       <c r="B35" t="n">
+        <v>201.34043856</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7454.737686979</v>
+      </c>
+      <c r="D35" t="n">
+        <v>140.633894493</v>
+      </c>
+      <c r="E35" t="n">
+        <v>189.498916573</v>
+      </c>
+      <c r="F35" t="n">
         <v>18451.834752001</v>
       </c>
-      <c r="C35" t="n">
+      <c r="G35" t="n">
         <v>11526.987959541</v>
       </c>
-      <c r="D35" t="n">
-        <v>7454.737686979</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="H35" t="n">
         <v>1126.965464347</v>
       </c>
-      <c r="F35" t="n">
-        <v>703.755090331</v>
-      </c>
-      <c r="G35" t="n">
-        <v>189.498916573</v>
-      </c>
-      <c r="H35" t="n">
-        <v>191.769493234</v>
+      <c r="I35" t="n">
+        <v>752.853752966</v>
       </c>
     </row>
     <row r="36">
@@ -1776,25 +1911,28 @@
         <v>43040</v>
       </c>
       <c r="B36" t="n">
+        <v>169.596858531</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11939.405171752</v>
+      </c>
+      <c r="D36" t="n">
+        <v>247.933329186</v>
+      </c>
+      <c r="E36" t="n">
+        <v>178.362697617</v>
+      </c>
+      <c r="F36" t="n">
         <v>18146.839934413</v>
       </c>
-      <c r="C36" t="n">
+      <c r="G36" t="n">
         <v>10753.782019884</v>
       </c>
-      <c r="D36" t="n">
-        <v>11939.405171752</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="H36" t="n">
         <v>1053.444615289</v>
       </c>
-      <c r="F36" t="n">
-        <v>696.179641639</v>
-      </c>
-      <c r="G36" t="n">
-        <v>178.362697617</v>
-      </c>
-      <c r="H36" t="n">
-        <v>369.483686557</v>
+      <c r="I36" t="n">
+        <v>947.6196477550001</v>
       </c>
     </row>
     <row r="37">
@@ -1802,25 +1940,28 @@
         <v>43070</v>
       </c>
       <c r="B37" t="n">
+        <v>175.965272977</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14490.547070046</v>
+      </c>
+      <c r="D37" t="n">
+        <v>321.185628835</v>
+      </c>
+      <c r="E37" t="n">
+        <v>156.237822481</v>
+      </c>
+      <c r="F37" t="n">
         <v>21083.448522348</v>
       </c>
-      <c r="C37" t="n">
+      <c r="G37" t="n">
         <v>9940.520323474</v>
       </c>
-      <c r="D37" t="n">
-        <v>14490.547070046</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="H37" t="n">
         <v>1113.490296544</v>
       </c>
-      <c r="F37" t="n">
-        <v>785.237631213</v>
-      </c>
-      <c r="G37" t="n">
-        <v>156.237822481</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1074.740226822</v>
+      <c r="I37" t="n">
+        <v>1657.873970901</v>
       </c>
     </row>
     <row r="38">
@@ -1828,25 +1969,28 @@
         <v>43101</v>
       </c>
       <c r="B38" t="n">
+        <v>185.4724958290001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>14796.051268462</v>
+      </c>
+      <c r="D38" t="n">
+        <v>299.7278536899999</v>
+      </c>
+      <c r="E38" t="n">
+        <v>171.416654035</v>
+      </c>
+      <c r="F38" t="n">
         <v>22361.21665608901</v>
       </c>
-      <c r="C38" t="n">
+      <c r="G38" t="n">
         <v>9356.809733287</v>
       </c>
-      <c r="D38" t="n">
-        <v>14796.051268462</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="H38" t="n">
         <v>1138.662524562</v>
       </c>
-      <c r="F38" t="n">
-        <v>787.577393505</v>
-      </c>
-      <c r="G38" t="n">
-        <v>171.416654035</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1338.755059063</v>
+      <c r="I38" t="n">
+        <v>2021.613223884</v>
       </c>
     </row>
     <row r="39">
@@ -1854,25 +1998,28 @@
         <v>43132</v>
       </c>
       <c r="B39" t="n">
+        <v>168.094750058</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12093.750261898</v>
+      </c>
+      <c r="D39" t="n">
+        <v>257.932977033</v>
+      </c>
+      <c r="E39" t="n">
+        <v>206.7940658060001</v>
+      </c>
+      <c r="F39" t="n">
         <v>20119.565025376</v>
       </c>
-      <c r="C39" t="n">
+      <c r="G39" t="n">
         <v>8363.803456603</v>
       </c>
-      <c r="D39" t="n">
-        <v>12093.750261898</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="H39" t="n">
         <v>966.0790129639997</v>
       </c>
-      <c r="F39" t="n">
-        <v>694.7794699619999</v>
-      </c>
-      <c r="G39" t="n">
-        <v>206.7940658060001</v>
-      </c>
-      <c r="H39" t="n">
-        <v>829.3816880070002</v>
+      <c r="I39" t="n">
+        <v>1397.145172274</v>
       </c>
     </row>
     <row r="40">
@@ -1880,25 +2027,28 @@
         <v>43160</v>
       </c>
       <c r="B40" t="n">
+        <v>161.5320972549999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13429.538697122</v>
+      </c>
+      <c r="D40" t="n">
+        <v>243.14381749</v>
+      </c>
+      <c r="E40" t="n">
+        <v>262.190120057</v>
+      </c>
+      <c r="F40" t="n">
         <v>19001.869000104</v>
       </c>
-      <c r="C40" t="n">
+      <c r="G40" t="n">
         <v>8793.831881535998</v>
       </c>
-      <c r="D40" t="n">
-        <v>13429.538697122</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="H40" t="n">
         <v>1057.486285579</v>
       </c>
-      <c r="F40" t="n">
-        <v>703.334240919</v>
-      </c>
-      <c r="G40" t="n">
-        <v>262.190120057</v>
-      </c>
-      <c r="H40" t="n">
-        <v>817.3782173369999</v>
+      <c r="I40" t="n">
+        <v>1469.934320339</v>
       </c>
     </row>
     <row r="41">
@@ -1906,25 +2056,28 @@
         <v>43191</v>
       </c>
       <c r="B41" t="n">
+        <v>216.706231212</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12531.93681319601</v>
+      </c>
+      <c r="D41" t="n">
+        <v>242.3457860300001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>284.4525297959996</v>
+      </c>
+      <c r="F41" t="n">
         <v>16445.85280270601</v>
       </c>
-      <c r="C41" t="n">
+      <c r="G41" t="n">
         <v>8976.072324684001</v>
       </c>
-      <c r="D41" t="n">
-        <v>12531.93681319601</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="H41" t="n">
         <v>1042.073344533</v>
       </c>
-      <c r="F41" t="n">
-        <v>737.1574426110001</v>
-      </c>
-      <c r="G41" t="n">
-        <v>284.4525297959996</v>
-      </c>
-      <c r="H41" t="n">
-        <v>219.204793972</v>
+      <c r="I41" t="n">
+        <v>883.1375091699999</v>
       </c>
     </row>
     <row r="42">
@@ -1932,25 +2085,28 @@
         <v>43221</v>
       </c>
       <c r="B42" t="n">
+        <v>467.98272818</v>
+      </c>
+      <c r="C42" t="n">
+        <v>11331.027309367</v>
+      </c>
+      <c r="D42" t="n">
+        <v>209.458661362</v>
+      </c>
+      <c r="E42" t="n">
+        <v>278.0993999250003</v>
+      </c>
+      <c r="F42" t="n">
         <v>16704.26764803</v>
       </c>
-      <c r="C42" t="n">
+      <c r="G42" t="n">
         <v>10841.651676305</v>
       </c>
-      <c r="D42" t="n">
-        <v>11331.027309367</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="H42" t="n">
         <v>969.0405564629999</v>
       </c>
-      <c r="F42" t="n">
-        <v>991.255457267</v>
-      </c>
-      <c r="G42" t="n">
-        <v>278.0993999250003</v>
-      </c>
-      <c r="H42" t="n">
-        <v>329.825120286</v>
+      <c r="I42" t="n">
+        <v>924.5226219499999</v>
       </c>
     </row>
     <row r="43">
@@ -1958,25 +2114,28 @@
         <v>43252</v>
       </c>
       <c r="B43" t="n">
+        <v>405.6686926240001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11444.993556614</v>
+      </c>
+      <c r="D43" t="n">
+        <v>103.0870558420001</v>
+      </c>
+      <c r="E43" t="n">
+        <v>292.1864294030003</v>
+      </c>
+      <c r="F43" t="n">
         <v>16903.95861356</v>
       </c>
-      <c r="C43" t="n">
+      <c r="G43" t="n">
         <v>10782.135578223</v>
       </c>
-      <c r="D43" t="n">
-        <v>11444.993556614</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="H43" t="n">
         <v>1111.241353049</v>
       </c>
-      <c r="F43" t="n">
-        <v>828.9714403280002</v>
-      </c>
-      <c r="G43" t="n">
-        <v>292.1864294030003</v>
-      </c>
-      <c r="H43" t="n">
-        <v>303.32025275</v>
+      <c r="I43" t="n">
+        <v>838.960109437</v>
       </c>
     </row>
     <row r="44">
@@ -1984,25 +2143,28 @@
         <v>43282</v>
       </c>
       <c r="B44" t="n">
+        <v>407.99152503</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12074.60692736599</v>
+      </c>
+      <c r="D44" t="n">
+        <v>131.83613027</v>
+      </c>
+      <c r="E44" t="n">
+        <v>315.5337598170001</v>
+      </c>
+      <c r="F44" t="n">
         <v>21243.377214383</v>
       </c>
-      <c r="C44" t="n">
+      <c r="G44" t="n">
         <v>12420.261264652</v>
       </c>
-      <c r="D44" t="n">
-        <v>12074.60692736599</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="H44" t="n">
         <v>1153.307986896</v>
       </c>
-      <c r="F44" t="n">
-        <v>936.1281614840001</v>
-      </c>
-      <c r="G44" t="n">
-        <v>315.5337598170001</v>
-      </c>
-      <c r="H44" t="n">
-        <v>620.450209607</v>
+      <c r="I44" t="n">
+        <v>1243.628366517</v>
       </c>
     </row>
     <row r="45">
@@ -2010,25 +2172,28 @@
         <v>43313</v>
       </c>
       <c r="B45" t="n">
+        <v>267.3169417949999</v>
+      </c>
+      <c r="C45" t="n">
+        <v>12220.738548954</v>
+      </c>
+      <c r="D45" t="n">
+        <v>141.93483804</v>
+      </c>
+      <c r="E45" t="n">
+        <v>290.8389810729998</v>
+      </c>
+      <c r="F45" t="n">
         <v>22380.238166706</v>
       </c>
-      <c r="C45" t="n">
+      <c r="G45" t="n">
         <v>12115.215005832</v>
       </c>
-      <c r="D45" t="n">
-        <v>12220.738548954</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="H45" t="n">
         <v>1130.234685872</v>
       </c>
-      <c r="F45" t="n">
-        <v>836.9404925629998</v>
-      </c>
-      <c r="G45" t="n">
-        <v>290.8389810729998</v>
-      </c>
-      <c r="H45" t="n">
-        <v>678.1359579089999</v>
+      <c r="I45" t="n">
+        <v>1486.253475334</v>
       </c>
     </row>
     <row r="46">
@@ -2036,25 +2201,28 @@
         <v>43344</v>
       </c>
       <c r="B46" t="n">
+        <v>334.9994649179999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8372.013956496998</v>
+      </c>
+      <c r="D46" t="n">
+        <v>157.6808314119999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>256.0711943260002</v>
+      </c>
+      <c r="F46" t="n">
         <v>19124.21633118</v>
       </c>
-      <c r="C46" t="n">
+      <c r="G46" t="n">
         <v>10529.199568105</v>
       </c>
-      <c r="D46" t="n">
-        <v>8372.013956496998</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="H46" t="n">
         <v>1174.409416499</v>
       </c>
-      <c r="F46" t="n">
-        <v>865.5757003439996</v>
-      </c>
-      <c r="G46" t="n">
-        <v>256.0711943260002</v>
-      </c>
-      <c r="H46" t="n">
-        <v>215.340033577</v>
+      <c r="I46" t="n">
+        <v>969.569915233</v>
       </c>
     </row>
     <row r="47">
@@ -2062,25 +2230,28 @@
         <v>43374</v>
       </c>
       <c r="B47" t="n">
+        <v>222.105155547</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10768.769659649</v>
+      </c>
+      <c r="D47" t="n">
+        <v>220.88584192</v>
+      </c>
+      <c r="E47" t="n">
+        <v>287.1864853849999</v>
+      </c>
+      <c r="F47" t="n">
         <v>16873.181279303</v>
       </c>
-      <c r="C47" t="n">
+      <c r="G47" t="n">
         <v>11498.298221175</v>
       </c>
-      <c r="D47" t="n">
-        <v>10768.769659649</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="H47" t="n">
         <v>1156.479775076</v>
       </c>
-      <c r="F47" t="n">
-        <v>730.047356734</v>
-      </c>
-      <c r="G47" t="n">
-        <v>287.1864853849999</v>
-      </c>
-      <c r="H47" t="n">
-        <v>482.2047298790001</v>
+      <c r="I47" t="n">
+        <v>1090.154650803</v>
       </c>
     </row>
     <row r="48">
@@ -2088,25 +2259,28 @@
         <v>43405</v>
       </c>
       <c r="B48" t="n">
+        <v>229.6950191779999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>11417.26173575</v>
+      </c>
+      <c r="D48" t="n">
+        <v>142.530039108</v>
+      </c>
+      <c r="E48" t="n">
+        <v>220.633496639</v>
+      </c>
+      <c r="F48" t="n">
         <v>17655.92117754</v>
       </c>
-      <c r="C48" t="n">
+      <c r="G48" t="n">
         <v>11571.539009496</v>
       </c>
-      <c r="D48" t="n">
-        <v>11417.26173575</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>1152.347765017</v>
       </c>
-      <c r="F48" t="n">
-        <v>669.818320894</v>
-      </c>
-      <c r="G48" t="n">
-        <v>220.633496639</v>
-      </c>
-      <c r="H48" t="n">
-        <v>260.970367433</v>
+      <c r="I48" t="n">
+        <v>994.008083187</v>
       </c>
     </row>
     <row r="49">
@@ -2114,25 +2288,28 @@
         <v>43435</v>
       </c>
       <c r="B49" t="n">
+        <v>259.6160271790001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>13586.134145588</v>
+      </c>
+      <c r="D49" t="n">
+        <v>305.806750639</v>
+      </c>
+      <c r="E49" t="n">
+        <v>198.7434431760007</v>
+      </c>
+      <c r="F49" t="n">
         <v>20536.400779153</v>
       </c>
-      <c r="C49" t="n">
+      <c r="G49" t="n">
         <v>11828.701768837</v>
       </c>
-      <c r="D49" t="n">
-        <v>13586.134145588</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>1212.140390228</v>
       </c>
-      <c r="F49" t="n">
-        <v>900.4717789370002</v>
-      </c>
-      <c r="G49" t="n">
-        <v>198.7434431760007</v>
-      </c>
-      <c r="H49" t="n">
-        <v>466.8379172510001</v>
+      <c r="I49" t="n">
+        <v>1136.295399841</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2317,28 @@
         <v>43466</v>
       </c>
       <c r="B50" t="n">
+        <v>200.360450594</v>
+      </c>
+      <c r="C50" t="n">
+        <v>14053.284033774</v>
+      </c>
+      <c r="D50" t="n">
+        <v>346.385302994</v>
+      </c>
+      <c r="E50" t="n">
+        <v>253.3458973920001</v>
+      </c>
+      <c r="F50" t="n">
         <v>21301.274729647</v>
       </c>
-      <c r="C50" t="n">
+      <c r="G50" t="n">
         <v>11663.001998099</v>
       </c>
-      <c r="D50" t="n">
-        <v>14053.284033774</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
         <v>1137.650978737</v>
       </c>
-      <c r="F50" t="n">
-        <v>886.363019977</v>
-      </c>
-      <c r="G50" t="n">
-        <v>253.3458973920001</v>
-      </c>
-      <c r="H50" t="n">
-        <v>627.562989564</v>
+      <c r="I50" t="n">
+        <v>1233.070305138</v>
       </c>
     </row>
     <row r="51">
@@ -2166,25 +2346,28 @@
         <v>43497</v>
       </c>
       <c r="B51" t="n">
+        <v>169.2812444940001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>11165.221094893</v>
+      </c>
+      <c r="D51" t="n">
+        <v>245.14764201</v>
+      </c>
+      <c r="E51" t="n">
+        <v>260.5333082850001</v>
+      </c>
+      <c r="F51" t="n">
         <v>17814.140197197</v>
       </c>
-      <c r="C51" t="n">
+      <c r="G51" t="n">
         <v>10501.404987137</v>
       </c>
-      <c r="D51" t="n">
-        <v>11165.221094893</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="H51" t="n">
         <v>1015.211580086</v>
       </c>
-      <c r="F51" t="n">
-        <v>712.3840653180001</v>
-      </c>
-      <c r="G51" t="n">
-        <v>260.5333082850001</v>
-      </c>
-      <c r="H51" t="n">
-        <v>385.4200814319999</v>
+      <c r="I51" t="n">
+        <v>929.056405786</v>
       </c>
     </row>
     <row r="52">
@@ -2192,25 +2375,28 @@
         <v>43525</v>
       </c>
       <c r="B52" t="n">
+        <v>173.204335347</v>
+      </c>
+      <c r="C52" t="n">
+        <v>11695.638599585</v>
+      </c>
+      <c r="D52" t="n">
+        <v>287.2032325290001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>347.8984672900003</v>
+      </c>
+      <c r="F52" t="n">
         <v>15982.09405901</v>
       </c>
-      <c r="C52" t="n">
+      <c r="G52" t="n">
         <v>13369.098682136</v>
       </c>
-      <c r="D52" t="n">
-        <v>11695.638599585</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="H52" t="n">
         <v>1307.404754804</v>
       </c>
-      <c r="F52" t="n">
-        <v>734.1361019170001</v>
-      </c>
-      <c r="G52" t="n">
-        <v>347.8984672900003</v>
-      </c>
-      <c r="H52" t="n">
-        <v>790.000299938</v>
+      <c r="I52" t="n">
+        <v>1323.836236241</v>
       </c>
     </row>
     <row r="53">
@@ -2218,25 +2404,28 @@
         <v>43556</v>
       </c>
       <c r="B53" t="n">
+        <v>241.1429919099999</v>
+      </c>
+      <c r="C53" t="n">
+        <v>11292.775368549</v>
+      </c>
+      <c r="D53" t="n">
+        <v>179.342255653</v>
+      </c>
+      <c r="E53" t="n">
+        <v>336.0097671589999</v>
+      </c>
+      <c r="F53" t="n">
         <v>13926.774591609</v>
       </c>
-      <c r="C53" t="n">
+      <c r="G53" t="n">
         <v>13471.231964398</v>
       </c>
-      <c r="D53" t="n">
-        <v>11292.775368549</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="H53" t="n">
         <v>1211.724377448</v>
       </c>
-      <c r="F53" t="n">
-        <v>704.1884331039998</v>
-      </c>
-      <c r="G53" t="n">
-        <v>336.0097671589999</v>
-      </c>
-      <c r="H53" t="n">
-        <v>225.609198136</v>
+      <c r="I53" t="n">
+        <v>770.4442290740001</v>
       </c>
     </row>
     <row r="54">
@@ -2244,25 +2433,28 @@
         <v>43586</v>
       </c>
       <c r="B54" t="n">
+        <v>277.5278932069999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10166.975058717</v>
+      </c>
+      <c r="D54" t="n">
+        <v>222.8451693750001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>445.4262954819998</v>
+      </c>
+      <c r="F54" t="n">
         <v>14361.235774443</v>
       </c>
-      <c r="C54" t="n">
+      <c r="G54" t="n">
         <v>14050.561939656</v>
       </c>
-      <c r="D54" t="n">
-        <v>10166.975058717</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
         <v>1205.116859807</v>
       </c>
-      <c r="F54" t="n">
-        <v>757.418427691</v>
-      </c>
-      <c r="G54" t="n">
-        <v>445.4262954819998</v>
-      </c>
-      <c r="H54" t="n">
-        <v>188.087989838</v>
+      <c r="I54" t="n">
+        <v>756.655735791</v>
       </c>
     </row>
     <row r="55">
@@ -2270,25 +2462,28 @@
         <v>43617</v>
       </c>
       <c r="B55" t="n">
+        <v>253.8525275999999</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8997.376775838004</v>
+      </c>
+      <c r="D55" t="n">
+        <v>101.588829643</v>
+      </c>
+      <c r="E55" t="n">
+        <v>374.1981788060004</v>
+      </c>
+      <c r="F55" t="n">
         <v>16641.571791543</v>
       </c>
-      <c r="C55" t="n">
+      <c r="G55" t="n">
         <v>12934.359284383</v>
       </c>
-      <c r="D55" t="n">
-        <v>8997.376775838004</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="H55" t="n">
         <v>1129.545127712</v>
       </c>
-      <c r="F55" t="n">
-        <v>577.2310677209998</v>
-      </c>
-      <c r="G55" t="n">
-        <v>374.1981788060004</v>
-      </c>
-      <c r="H55" t="n">
-        <v>195.489303919</v>
+      <c r="I55" t="n">
+        <v>713.335912989</v>
       </c>
     </row>
     <row r="56">
@@ -2296,25 +2491,28 @@
         <v>43647</v>
       </c>
       <c r="B56" t="n">
+        <v>256.0935804439999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>11751.02448308</v>
+      </c>
+      <c r="D56" t="n">
+        <v>187.4205343140001</v>
+      </c>
+      <c r="E56" t="n">
+        <v>320.0266426839997</v>
+      </c>
+      <c r="F56" t="n">
         <v>21058.300003996</v>
       </c>
-      <c r="C56" t="n">
+      <c r="G56" t="n">
         <v>11110.340196961</v>
       </c>
-      <c r="D56" t="n">
-        <v>11751.02448308</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
         <v>1347.255031649</v>
       </c>
-      <c r="F56" t="n">
-        <v>749.478151366</v>
-      </c>
-      <c r="G56" t="n">
-        <v>320.0266426839997</v>
-      </c>
-      <c r="H56" t="n">
-        <v>212.043965433</v>
+      <c r="I56" t="n">
+        <v>770.964710427</v>
       </c>
     </row>
     <row r="57">
@@ -2322,25 +2520,28 @@
         <v>43678</v>
       </c>
       <c r="B57" t="n">
+        <v>281.317686776</v>
+      </c>
+      <c r="C57" t="n">
+        <v>12083.058487263</v>
+      </c>
+      <c r="D57" t="n">
+        <v>145.9204217999999</v>
+      </c>
+      <c r="E57" t="n">
+        <v>374.787545005998</v>
+      </c>
+      <c r="F57" t="n">
         <v>21642.59268432499</v>
       </c>
-      <c r="C57" t="n">
+      <c r="G57" t="n">
         <v>11597.152778813</v>
       </c>
-      <c r="D57" t="n">
-        <v>12083.058487263</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="H57" t="n">
         <v>1339.555704855</v>
       </c>
-      <c r="F57" t="n">
-        <v>740.3078821189999</v>
-      </c>
-      <c r="G57" t="n">
-        <v>374.787545005998</v>
-      </c>
-      <c r="H57" t="n">
-        <v>257.756013682</v>
+      <c r="I57" t="n">
+        <v>1007.431183331</v>
       </c>
     </row>
     <row r="58">
@@ -2348,25 +2549,28 @@
         <v>43709</v>
       </c>
       <c r="B58" t="n">
+        <v>260.6759190989999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>9623.030599402</v>
+      </c>
+      <c r="D58" t="n">
+        <v>134.480084778</v>
+      </c>
+      <c r="E58" t="n">
+        <v>285.0288618590005</v>
+      </c>
+      <c r="F58" t="n">
         <v>19787.846636922</v>
       </c>
-      <c r="C58" t="n">
+      <c r="G58" t="n">
         <v>9803.380330612998</v>
       </c>
-      <c r="D58" t="n">
-        <v>9623.030599402</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>1027.542571907</v>
       </c>
-      <c r="F58" t="n">
-        <v>693.9064268849999</v>
-      </c>
-      <c r="G58" t="n">
-        <v>285.0288618590005</v>
-      </c>
-      <c r="H58" t="n">
-        <v>100.483229309</v>
+      <c r="I58" t="n">
+        <v>853.840686323</v>
       </c>
     </row>
     <row r="59">
@@ -2374,25 +2578,28 @@
         <v>43739</v>
       </c>
       <c r="B59" t="n">
+        <v>249.8059578389999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>9856.481216391001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>227.3678482810001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>334.0373826830008</v>
+      </c>
+      <c r="F59" t="n">
         <v>18845.07292393601</v>
       </c>
-      <c r="C59" t="n">
+      <c r="G59" t="n">
         <v>10070.763229009</v>
       </c>
-      <c r="D59" t="n">
-        <v>9856.481216391001</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="H59" t="n">
         <v>384.131505375</v>
       </c>
-      <c r="F59" t="n">
-        <v>767.174011948</v>
-      </c>
-      <c r="G59" t="n">
-        <v>334.0373826830008</v>
-      </c>
-      <c r="H59" t="n">
-        <v>191.2403966979999</v>
+      <c r="I59" t="n">
+        <v>1603.150922087</v>
       </c>
     </row>
     <row r="60">
@@ -2400,25 +2607,28 @@
         <v>43770</v>
       </c>
       <c r="B60" t="n">
+        <v>180.976146164</v>
+      </c>
+      <c r="C60" t="n">
+        <v>12203.360440227</v>
+      </c>
+      <c r="D60" t="n">
+        <v>253.788827959</v>
+      </c>
+      <c r="E60" t="n">
+        <v>278.2172301389994</v>
+      </c>
+      <c r="F60" t="n">
         <v>18101.409566727</v>
       </c>
-      <c r="C60" t="n">
+      <c r="G60" t="n">
         <v>9724.402357144998</v>
       </c>
-      <c r="D60" t="n">
-        <v>12203.360440227</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="H60" t="n">
         <v>378.547283361</v>
       </c>
-      <c r="F60" t="n">
-        <v>701.010431014</v>
-      </c>
-      <c r="G60" t="n">
-        <v>278.2172301389994</v>
-      </c>
-      <c r="H60" t="n">
-        <v>152.931599551</v>
+      <c r="I60" t="n">
+        <v>1450.821895426</v>
       </c>
     </row>
     <row r="61">
@@ -2426,25 +2636,28 @@
         <v>43800</v>
       </c>
       <c r="B61" t="n">
+        <v>194.808774629</v>
+      </c>
+      <c r="C61" t="n">
+        <v>16002.87832364699</v>
+      </c>
+      <c r="D61" t="n">
+        <v>340.8678839890001</v>
+      </c>
+      <c r="E61" t="n">
+        <v>241.3579110239997</v>
+      </c>
+      <c r="F61" t="n">
         <v>18153.42290757799</v>
       </c>
-      <c r="C61" t="n">
+      <c r="G61" t="n">
         <v>10513.642438245</v>
       </c>
-      <c r="D61" t="n">
-        <v>16002.87832364699</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="H61" t="n">
         <v>423.1381672190001</v>
       </c>
-      <c r="F61" t="n">
-        <v>835.9050086060001</v>
-      </c>
-      <c r="G61" t="n">
-        <v>241.3579110239997</v>
-      </c>
-      <c r="H61" t="n">
-        <v>642.63426014</v>
+      <c r="I61" t="n">
+        <v>1953.9562478</v>
       </c>
     </row>
     <row r="62">
@@ -2452,25 +2665,28 @@
         <v>43831</v>
       </c>
       <c r="B62" t="n">
+        <v>221.183070665</v>
+      </c>
+      <c r="C62" t="n">
+        <v>15241.871166649</v>
+      </c>
+      <c r="D62" t="n">
+        <v>310.782841122</v>
+      </c>
+      <c r="E62" t="n">
+        <v>247.4263244939999</v>
+      </c>
+      <c r="F62" t="n">
         <v>17659.970028376</v>
       </c>
-      <c r="C62" t="n">
+      <c r="G62" t="n">
         <v>11314.741917172</v>
       </c>
-      <c r="D62" t="n">
-        <v>15241.871166649</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="H62" t="n">
         <v>322.9276259819999</v>
       </c>
-      <c r="F62" t="n">
-        <v>843.857490549</v>
-      </c>
-      <c r="G62" t="n">
-        <v>247.4263244939999</v>
-      </c>
-      <c r="H62" t="n">
-        <v>277.253994019</v>
+      <c r="I62" t="n">
+        <v>1718.608532127</v>
       </c>
     </row>
     <row r="63">
@@ -2478,25 +2694,28 @@
         <v>43862</v>
       </c>
       <c r="B63" t="n">
+        <v>204.010758844</v>
+      </c>
+      <c r="C63" t="n">
+        <v>13445.034058922</v>
+      </c>
+      <c r="D63" t="n">
+        <v>292.0927346479999</v>
+      </c>
+      <c r="E63" t="n">
+        <v>341.1895969389988</v>
+      </c>
+      <c r="F63" t="n">
         <v>15498.038471075</v>
       </c>
-      <c r="C63" t="n">
+      <c r="G63" t="n">
         <v>12086.887998179</v>
       </c>
-      <c r="D63" t="n">
-        <v>13445.034058922</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="H63" t="n">
         <v>359.278824161</v>
       </c>
-      <c r="F63" t="n">
-        <v>814.7755591779999</v>
-      </c>
-      <c r="G63" t="n">
-        <v>341.1895969389988</v>
-      </c>
-      <c r="H63" t="n">
-        <v>84.216655824</v>
+      <c r="I63" t="n">
+        <v>1516.969199379</v>
       </c>
     </row>
     <row r="64">
@@ -2504,25 +2723,28 @@
         <v>43891</v>
       </c>
       <c r="B64" t="n">
+        <v>227.2484526109999</v>
+      </c>
+      <c r="C64" t="n">
+        <v>13161.505267132</v>
+      </c>
+      <c r="D64" t="n">
+        <v>301.554531003</v>
+      </c>
+      <c r="E64" t="n">
+        <v>506.265294763001</v>
+      </c>
+      <c r="F64" t="n">
         <v>13177.284309514</v>
       </c>
-      <c r="C64" t="n">
+      <c r="G64" t="n">
         <v>13788.468427867</v>
       </c>
-      <c r="D64" t="n">
-        <v>13161.505267132</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="H64" t="n">
         <v>405.0297271699999</v>
       </c>
-      <c r="F64" t="n">
-        <v>829.9491196189999</v>
-      </c>
-      <c r="G64" t="n">
-        <v>506.265294763001</v>
-      </c>
-      <c r="H64" t="n">
-        <v>88.08439490500001</v>
+      <c r="I64" t="n">
+        <v>1591.880184221</v>
       </c>
     </row>
     <row r="65">
@@ -2530,25 +2752,28 @@
         <v>43922</v>
       </c>
       <c r="B65" t="n">
+        <v>210.183405124</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9013.709972488998</v>
+      </c>
+      <c r="D65" t="n">
+        <v>309.3151087160002</v>
+      </c>
+      <c r="E65" t="n">
+        <v>571.8388447119985</v>
+      </c>
+      <c r="F65" t="n">
         <v>14110.04387748001</v>
       </c>
-      <c r="C65" t="n">
+      <c r="G65" t="n">
         <v>13049.335517526</v>
       </c>
-      <c r="D65" t="n">
-        <v>9013.709972488998</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="H65" t="n">
         <v>337.731956659</v>
       </c>
-      <c r="F65" t="n">
-        <v>815.7831568960003</v>
-      </c>
-      <c r="G65" t="n">
-        <v>571.8388447119985</v>
-      </c>
-      <c r="H65" t="n">
-        <v>111.727313229</v>
+      <c r="I65" t="n">
+        <v>1565.288259872</v>
       </c>
     </row>
     <row r="66">
@@ -2556,25 +2781,28 @@
         <v>43952</v>
       </c>
       <c r="B66" t="n">
+        <v>270.9514062489998</v>
+      </c>
+      <c r="C66" t="n">
+        <v>7251.384697279</v>
+      </c>
+      <c r="D66" t="n">
+        <v>215.98303828</v>
+      </c>
+      <c r="E66" t="n">
+        <v>497.5797159209995</v>
+      </c>
+      <c r="F66" t="n">
         <v>14078.91714728199</v>
       </c>
-      <c r="C66" t="n">
+      <c r="G66" t="n">
         <v>14555.453434285</v>
       </c>
-      <c r="D66" t="n">
-        <v>7251.384697279</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="H66" t="n">
         <v>309.0807447589999</v>
       </c>
-      <c r="F66" t="n">
-        <v>772.6754992929998</v>
-      </c>
-      <c r="G66" t="n">
-        <v>497.5797159209995</v>
-      </c>
-      <c r="H66" t="n">
-        <v>23.756327334</v>
+      <c r="I66" t="n">
+        <v>1404.14547589</v>
       </c>
     </row>
     <row r="67">
@@ -2582,25 +2810,28 @@
         <v>43983</v>
       </c>
       <c r="B67" t="n">
+        <v>283.4472251469999</v>
+      </c>
+      <c r="C67" t="n">
+        <v>9057.534519388999</v>
+      </c>
+      <c r="D67" t="n">
+        <v>155.165004906</v>
+      </c>
+      <c r="E67" t="n">
+        <v>489.4840890909982</v>
+      </c>
+      <c r="F67" t="n">
         <v>15596.866136842</v>
       </c>
-      <c r="C67" t="n">
+      <c r="G67" t="n">
         <v>13408.67087168</v>
       </c>
-      <c r="D67" t="n">
-        <v>9057.534519388999</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="H67" t="n">
         <v>302.7455383519999</v>
       </c>
-      <c r="F67" t="n">
-        <v>662.9296158999999</v>
-      </c>
-      <c r="G67" t="n">
-        <v>489.4840890909982</v>
-      </c>
-      <c r="H67" t="n">
-        <v>28.56740172</v>
+      <c r="I67" t="n">
+        <v>1411.491680938</v>
       </c>
     </row>
     <row r="68">
@@ -2608,25 +2839,28 @@
         <v>44013</v>
       </c>
       <c r="B68" t="n">
+        <v>368.6893270709996</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10065.418399721</v>
+      </c>
+      <c r="D68" t="n">
+        <v>157.043839688</v>
+      </c>
+      <c r="E68" t="n">
+        <v>370.8686091789999</v>
+      </c>
+      <c r="F68" t="n">
         <v>17943.314497787</v>
       </c>
-      <c r="C68" t="n">
+      <c r="G68" t="n">
         <v>13069.346632455</v>
       </c>
-      <c r="D68" t="n">
-        <v>10065.418399721</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="H68" t="n">
         <v>353.7311723110001</v>
       </c>
-      <c r="F68" t="n">
-        <v>762.1054439379996</v>
-      </c>
-      <c r="G68" t="n">
-        <v>370.8686091789999</v>
-      </c>
-      <c r="H68" t="n">
-        <v>21.160154028</v>
+      <c r="I68" t="n">
+        <v>1419.147620233</v>
       </c>
     </row>
     <row r="69">
@@ -2634,25 +2868,28 @@
         <v>44044</v>
       </c>
       <c r="B69" t="n">
+        <v>789.5127536510004</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12776.954461065</v>
+      </c>
+      <c r="D69" t="n">
+        <v>252.289765644</v>
+      </c>
+      <c r="E69" t="n">
+        <v>430.9854229080006</v>
+      </c>
+      <c r="F69" t="n">
         <v>19433.720829381</v>
       </c>
-      <c r="C69" t="n">
+      <c r="G69" t="n">
         <v>11925.927536944</v>
       </c>
-      <c r="D69" t="n">
-        <v>12776.954461065</v>
-      </c>
-      <c r="E69" t="n">
+      <c r="H69" t="n">
         <v>478.714206109</v>
       </c>
-      <c r="F69" t="n">
-        <v>1312.74407547</v>
-      </c>
-      <c r="G69" t="n">
-        <v>430.9854229080006</v>
-      </c>
-      <c r="H69" t="n">
-        <v>136.04949385</v>
+      <c r="I69" t="n">
+        <v>1618.136700993</v>
       </c>
     </row>
     <row r="70">
@@ -2660,25 +2897,28 @@
         <v>44075</v>
       </c>
       <c r="B70" t="n">
+        <v>619.664418144</v>
+      </c>
+      <c r="C70" t="n">
+        <v>11519.99410228</v>
+      </c>
+      <c r="D70" t="n">
+        <v>188.751321582</v>
+      </c>
+      <c r="E70" t="n">
+        <v>424.1593847190002</v>
+      </c>
+      <c r="F70" t="n">
         <v>17416.301111253</v>
       </c>
-      <c r="C70" t="n">
+      <c r="G70" t="n">
         <v>8835.019102794</v>
       </c>
-      <c r="D70" t="n">
-        <v>11519.99410228</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="H70" t="n">
         <v>507.1568046970001</v>
       </c>
-      <c r="F70" t="n">
-        <v>1058.498082545</v>
-      </c>
-      <c r="G70" t="n">
-        <v>424.1593847190002</v>
-      </c>
-      <c r="H70" t="n">
-        <v>512.299530116</v>
+      <c r="I70" t="n">
+        <v>1958.090243251</v>
       </c>
     </row>
     <row r="71">
@@ -2686,25 +2926,28 @@
         <v>44105</v>
       </c>
       <c r="B71" t="n">
+        <v>226.8260773140001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>11002.461171554</v>
+      </c>
+      <c r="D71" t="n">
+        <v>229.671584345</v>
+      </c>
+      <c r="E71" t="n">
+        <v>496.719031356</v>
+      </c>
+      <c r="F71" t="n">
         <v>13590.80763767101</v>
       </c>
-      <c r="C71" t="n">
+      <c r="G71" t="n">
         <v>12811.638874599</v>
       </c>
-      <c r="D71" t="n">
-        <v>11002.461171554</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="H71" t="n">
         <v>377.8828084069999</v>
       </c>
-      <c r="F71" t="n">
-        <v>699.017677219</v>
-      </c>
-      <c r="G71" t="n">
-        <v>496.719031356</v>
-      </c>
-      <c r="H71" t="n">
-        <v>140.115512465</v>
+      <c r="I71" t="n">
+        <v>1241.453073689</v>
       </c>
     </row>
     <row r="72">
@@ -2712,25 +2955,28 @@
         <v>44136</v>
       </c>
       <c r="B72" t="n">
+        <v>198.8080540900001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>12322.758230948</v>
+      </c>
+      <c r="D72" t="n">
+        <v>321.649843441</v>
+      </c>
+      <c r="E72" t="n">
+        <v>361.4892584349997</v>
+      </c>
+      <c r="F72" t="n">
         <v>13799.299382751</v>
       </c>
-      <c r="C72" t="n">
+      <c r="G72" t="n">
         <v>13383.711885612</v>
       </c>
-      <c r="D72" t="n">
-        <v>12322.758230948</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="H72" t="n">
         <v>420.396962251</v>
       </c>
-      <c r="F72" t="n">
-        <v>742.5429944340001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>361.4892584349997</v>
-      </c>
-      <c r="H72" t="n">
-        <v>321.216882334</v>
+      <c r="I72" t="n">
+        <v>1290.856345802</v>
       </c>
     </row>
     <row r="73">
@@ -2738,25 +2984,28 @@
         <v>44166</v>
       </c>
       <c r="B73" t="n">
+        <v>190.049498488</v>
+      </c>
+      <c r="C73" t="n">
+        <v>16155.12883243299</v>
+      </c>
+      <c r="D73" t="n">
+        <v>400.086130952</v>
+      </c>
+      <c r="E73" t="n">
+        <v>341.5257870779998</v>
+      </c>
+      <c r="F73" t="n">
         <v>15076.533304186</v>
       </c>
-      <c r="C73" t="n">
+      <c r="G73" t="n">
         <v>14353.736296226</v>
       </c>
-      <c r="D73" t="n">
-        <v>16155.12883243299</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="H73" t="n">
         <v>477.1828974089998</v>
       </c>
-      <c r="F73" t="n">
-        <v>892.1998171590001</v>
-      </c>
-      <c r="G73" t="n">
-        <v>341.5257870779998</v>
-      </c>
-      <c r="H73" t="n">
-        <v>443.102943629</v>
+      <c r="I73" t="n">
+        <v>1592.731077755</v>
       </c>
     </row>
     <row r="74">
@@ -2764,25 +3013,28 @@
         <v>44197</v>
       </c>
       <c r="B74" t="n">
+        <v>189.563391999</v>
+      </c>
+      <c r="C74" t="n">
+        <v>16765.30283854</v>
+      </c>
+      <c r="D74" t="n">
+        <v>375.665015845</v>
+      </c>
+      <c r="E74" t="n">
+        <v>341.2341558789992</v>
+      </c>
+      <c r="F74" t="n">
         <v>16952.540236608</v>
       </c>
-      <c r="C74" t="n">
+      <c r="G74" t="n">
         <v>13391.909656631</v>
       </c>
-      <c r="D74" t="n">
-        <v>16765.30283854</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="H74" t="n">
         <v>461.961091187</v>
       </c>
-      <c r="F74" t="n">
-        <v>888.103879701</v>
-      </c>
-      <c r="G74" t="n">
-        <v>341.2341558789992</v>
-      </c>
-      <c r="H74" t="n">
-        <v>333.1236105550001</v>
+      <c r="I74" t="n">
+        <v>1530.9754274</v>
       </c>
     </row>
     <row r="75">
@@ -2790,25 +3042,28 @@
         <v>44228</v>
       </c>
       <c r="B75" t="n">
+        <v>166.9878236769999</v>
+      </c>
+      <c r="C75" t="n">
+        <v>13287.751734429</v>
+      </c>
+      <c r="D75" t="n">
+        <v>384.982810227</v>
+      </c>
+      <c r="E75" t="n">
+        <v>450.2398639319994</v>
+      </c>
+      <c r="F75" t="n">
         <v>13826.179224764</v>
       </c>
-      <c r="C75" t="n">
+      <c r="G75" t="n">
         <v>12132.702317416</v>
       </c>
-      <c r="D75" t="n">
-        <v>13287.751734429</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="H75" t="n">
         <v>430.6673402469999</v>
       </c>
-      <c r="F75" t="n">
-        <v>859.1428343329999</v>
-      </c>
-      <c r="G75" t="n">
-        <v>450.2398639319994</v>
-      </c>
-      <c r="H75" t="n">
-        <v>154.682937433</v>
+      <c r="I75" t="n">
+        <v>1264.590881803</v>
       </c>
     </row>
     <row r="76">
@@ -2816,25 +3071,28 @@
         <v>44256</v>
       </c>
       <c r="B76" t="n">
+        <v>197.1890692830001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>14982.765616539</v>
+      </c>
+      <c r="D76" t="n">
+        <v>268.9302192649999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>583.4454299599998</v>
+      </c>
+      <c r="F76" t="n">
         <v>12633.37892004601</v>
       </c>
-      <c r="C76" t="n">
+      <c r="G76" t="n">
         <v>13159.239635823</v>
       </c>
-      <c r="D76" t="n">
-        <v>14982.765616539</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="H76" t="n">
         <v>575.9217675870001</v>
       </c>
-      <c r="F76" t="n">
-        <v>774.026676525</v>
-      </c>
-      <c r="G76" t="n">
-        <v>583.4454299599998</v>
-      </c>
-      <c r="H76" t="n">
-        <v>77.438297166</v>
+      <c r="I76" t="n">
+        <v>1265.485351737</v>
       </c>
     </row>
     <row r="77">
@@ -2842,25 +3100,28 @@
         <v>44287</v>
       </c>
       <c r="B77" t="n">
+        <v>232.3564471900001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>13070.649872677</v>
+      </c>
+      <c r="D77" t="n">
+        <v>268.7092658440001</v>
+      </c>
+      <c r="E77" t="n">
+        <v>662.7228284899991</v>
+      </c>
+      <c r="F77" t="n">
         <v>12326.998439663</v>
       </c>
-      <c r="C77" t="n">
+      <c r="G77" t="n">
         <v>11965.764598351</v>
       </c>
-      <c r="D77" t="n">
-        <v>13070.649872677</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="H77" t="n">
         <v>532.2424898530001</v>
       </c>
-      <c r="F77" t="n">
-        <v>819.7359208580001</v>
-      </c>
-      <c r="G77" t="n">
-        <v>662.7228284899991</v>
-      </c>
-      <c r="H77" t="n">
-        <v>97.08549385999999</v>
+      <c r="I77" t="n">
+        <v>1258.825002247</v>
       </c>
     </row>
     <row r="78">
@@ -2868,25 +3129,28 @@
         <v>44317</v>
       </c>
       <c r="B78" t="n">
+        <v>327.6589062649999</v>
+      </c>
+      <c r="C78" t="n">
+        <v>11883.930876838</v>
+      </c>
+      <c r="D78" t="n">
+        <v>272.8394789330001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>634.4099167029993</v>
+      </c>
+      <c r="F78" t="n">
         <v>13908.068940125</v>
       </c>
-      <c r="C78" t="n">
+      <c r="G78" t="n">
         <v>12176.606138312</v>
       </c>
-      <c r="D78" t="n">
-        <v>11883.930876838</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="H78" t="n">
         <v>609.2789487479998</v>
       </c>
-      <c r="F78" t="n">
-        <v>902.917311269</v>
-      </c>
-      <c r="G78" t="n">
-        <v>634.4099167029993</v>
-      </c>
-      <c r="H78" t="n">
-        <v>220.674991196</v>
+      <c r="I78" t="n">
+        <v>1238.042140616</v>
       </c>
     </row>
     <row r="79">
@@ -2894,25 +3158,28 @@
         <v>44348</v>
       </c>
       <c r="B79" t="n">
+        <v>384.5163311219998</v>
+      </c>
+      <c r="C79" t="n">
+        <v>12980.242796874</v>
+      </c>
+      <c r="D79" t="n">
+        <v>130.032908324</v>
+      </c>
+      <c r="E79" t="n">
+        <v>633.2992791400001</v>
+      </c>
+      <c r="F79" t="n">
         <v>15952.265847382</v>
       </c>
-      <c r="C79" t="n">
+      <c r="G79" t="n">
         <v>10792.590283765</v>
       </c>
-      <c r="D79" t="n">
-        <v>12980.242796874</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="H79" t="n">
         <v>478.735672779</v>
       </c>
-      <c r="F79" t="n">
-        <v>809.2579748499998</v>
-      </c>
-      <c r="G79" t="n">
-        <v>633.2992791400001</v>
-      </c>
-      <c r="H79" t="n">
-        <v>169.954893629</v>
+      <c r="I79" t="n">
+        <v>1090.835491569</v>
       </c>
     </row>
     <row r="80">
@@ -2920,25 +3187,28 @@
         <v>44378</v>
       </c>
       <c r="B80" t="n">
+        <v>361.740003724</v>
+      </c>
+      <c r="C80" t="n">
+        <v>15270.24282910701</v>
+      </c>
+      <c r="D80" t="n">
+        <v>120.7975432779999</v>
+      </c>
+      <c r="E80" t="n">
+        <v>630.5560761010004</v>
+      </c>
+      <c r="F80" t="n">
         <v>20361.612474574</v>
       </c>
-      <c r="C80" t="n">
+      <c r="G80" t="n">
         <v>11704.354300943</v>
       </c>
-      <c r="D80" t="n">
-        <v>15270.24282910701</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="H80" t="n">
         <v>606.2821089400002</v>
       </c>
-      <c r="F80" t="n">
-        <v>825.2539919439999</v>
-      </c>
-      <c r="G80" t="n">
-        <v>630.5560761010004</v>
-      </c>
-      <c r="H80" t="n">
-        <v>261.137587117</v>
+      <c r="I80" t="n">
+        <v>1304.242284295</v>
       </c>
     </row>
     <row r="81">
@@ -2946,25 +3216,28 @@
         <v>44409</v>
       </c>
       <c r="B81" t="n">
+        <v>282.8406573410001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>13488.604606769</v>
+      </c>
+      <c r="D81" t="n">
+        <v>153.701195446</v>
+      </c>
+      <c r="E81" t="n">
+        <v>530.7683404940003</v>
+      </c>
+      <c r="F81" t="n">
         <v>19812.870308708</v>
       </c>
-      <c r="C81" t="n">
+      <c r="G81" t="n">
         <v>12139.694455367</v>
       </c>
-      <c r="D81" t="n">
-        <v>13488.604606769</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="H81" t="n">
         <v>593.3051077430002</v>
       </c>
-      <c r="F81" t="n">
-        <v>753.9016175050001</v>
-      </c>
-      <c r="G81" t="n">
-        <v>530.7683404940003</v>
-      </c>
-      <c r="H81" t="n">
-        <v>67.156485593</v>
+      <c r="I81" t="n">
+        <v>1253.231347999</v>
       </c>
     </row>
     <row r="82">
@@ -2972,25 +3245,28 @@
         <v>44440</v>
       </c>
       <c r="B82" t="n">
+        <v>291.3424518080002</v>
+      </c>
+      <c r="C82" t="n">
+        <v>12191.95821296</v>
+      </c>
+      <c r="D82" t="n">
+        <v>212.7738657970001</v>
+      </c>
+      <c r="E82" t="n">
+        <v>498.3933248320006</v>
+      </c>
+      <c r="F82" t="n">
         <v>15558.49057202401</v>
       </c>
-      <c r="C82" t="n">
+      <c r="G82" t="n">
         <v>11559.597665653</v>
       </c>
-      <c r="D82" t="n">
-        <v>12191.95821296</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="H82" t="n">
         <v>530.0649489870001</v>
       </c>
-      <c r="F82" t="n">
-        <v>780.3749866400003</v>
-      </c>
-      <c r="G82" t="n">
-        <v>498.3933248320006</v>
-      </c>
-      <c r="H82" t="n">
-        <v>202.097876227</v>
+      <c r="I82" t="n">
+        <v>1289.837006385</v>
       </c>
     </row>
     <row r="83">
@@ -2998,25 +3274,28 @@
         <v>44470</v>
       </c>
       <c r="B83" t="n">
+        <v>210.2356674850001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>12590.856591948</v>
+      </c>
+      <c r="D83" t="n">
+        <v>203.280126458</v>
+      </c>
+      <c r="E83" t="n">
+        <v>561.4429320449984</v>
+      </c>
+      <c r="F83" t="n">
         <v>14632.752860389</v>
       </c>
-      <c r="C83" t="n">
+      <c r="G83" t="n">
         <v>12789.14809968</v>
       </c>
-      <c r="D83" t="n">
-        <v>12590.856591948</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="H83" t="n">
         <v>535.8304449390001</v>
       </c>
-      <c r="F83" t="n">
-        <v>705.0189962200002</v>
-      </c>
-      <c r="G83" t="n">
-        <v>561.4429320449984</v>
-      </c>
-      <c r="H83" t="n">
-        <v>207.968874766</v>
+      <c r="I83" t="n">
+        <v>1256.632735587</v>
       </c>
     </row>
     <row r="84">
@@ -3024,25 +3303,28 @@
         <v>44501</v>
       </c>
       <c r="B84" t="n">
+        <v>173.967979516</v>
+      </c>
+      <c r="C84" t="n">
+        <v>12798.251296812</v>
+      </c>
+      <c r="D84" t="n">
+        <v>342.0870039659999</v>
+      </c>
+      <c r="E84" t="n">
+        <v>444.6040143090001</v>
+      </c>
+      <c r="F84" t="n">
         <v>15490.465928442</v>
       </c>
-      <c r="C84" t="n">
+      <c r="G84" t="n">
         <v>12903.931444396</v>
       </c>
-      <c r="D84" t="n">
-        <v>12798.251296812</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="H84" t="n">
         <v>473.2844579290001</v>
       </c>
-      <c r="F84" t="n">
-        <v>771.2576331589999</v>
-      </c>
-      <c r="G84" t="n">
-        <v>444.6040143090001</v>
-      </c>
-      <c r="H84" t="n">
-        <v>153.907468156</v>
+      <c r="I84" t="n">
+        <v>1229.880459479</v>
       </c>
     </row>
     <row r="85">
@@ -3050,25 +3332,28 @@
         <v>44531</v>
       </c>
       <c r="B85" t="n">
+        <v>177.42982248</v>
+      </c>
+      <c r="C85" t="n">
+        <v>14090.156066772</v>
+      </c>
+      <c r="D85" t="n">
+        <v>432.289745178</v>
+      </c>
+      <c r="E85" t="n">
+        <v>418.9741937450009</v>
+      </c>
+      <c r="F85" t="n">
         <v>17399.31538824399</v>
       </c>
-      <c r="C85" t="n">
+      <c r="G85" t="n">
         <v>15741.010455358</v>
       </c>
-      <c r="D85" t="n">
-        <v>14090.156066772</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="H85" t="n">
         <v>617.1697050670001</v>
       </c>
-      <c r="F85" t="n">
-        <v>947.006641486</v>
-      </c>
-      <c r="G85" t="n">
-        <v>418.9741937450009</v>
-      </c>
-      <c r="H85" t="n">
-        <v>169.299645265</v>
+      <c r="I85" t="n">
+        <v>1369.248414005</v>
       </c>
     </row>
     <row r="86">
@@ -3076,25 +3361,28 @@
         <v>44562</v>
       </c>
       <c r="B86" t="n">
+        <v>187.178583446</v>
+      </c>
+      <c r="C86" t="n">
+        <v>14972.427080693</v>
+      </c>
+      <c r="D86" t="n">
+        <v>344.581892163</v>
+      </c>
+      <c r="E86" t="n">
+        <v>541.1826981869992</v>
+      </c>
+      <c r="F86" t="n">
         <v>17767.670639246</v>
       </c>
-      <c r="C86" t="n">
+      <c r="G86" t="n">
         <v>15330.922149748</v>
       </c>
-      <c r="D86" t="n">
-        <v>14972.427080693</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="H86" t="n">
         <v>568.399823133</v>
       </c>
-      <c r="F86" t="n">
-        <v>861.211052272</v>
-      </c>
-      <c r="G86" t="n">
-        <v>541.1826981869992</v>
-      </c>
-      <c r="H86" t="n">
-        <v>454.7863726819999</v>
+      <c r="I86" t="n">
+        <v>1640.803129084</v>
       </c>
     </row>
     <row r="87">
@@ -3102,25 +3390,28 @@
         <v>44593</v>
       </c>
       <c r="B87" t="n">
+        <v>165.0734940390001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>13335.407803607</v>
+      </c>
+      <c r="D87" t="n">
+        <v>406.108149865</v>
+      </c>
+      <c r="E87" t="n">
+        <v>630.4649315829988</v>
+      </c>
+      <c r="F87" t="n">
         <v>15443.531473093</v>
       </c>
-      <c r="C87" t="n">
+      <c r="G87" t="n">
         <v>13313.981862711</v>
       </c>
-      <c r="D87" t="n">
-        <v>13335.407803607</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="H87" t="n">
         <v>572.452376816</v>
       </c>
-      <c r="F87" t="n">
-        <v>894.0354810550001</v>
-      </c>
-      <c r="G87" t="n">
-        <v>630.4649315829988</v>
-      </c>
-      <c r="H87" t="n">
-        <v>131.128967928</v>
+      <c r="I87" t="n">
+        <v>1249.831264991</v>
       </c>
     </row>
     <row r="88">
@@ -3128,25 +3419,28 @@
         <v>44621</v>
       </c>
       <c r="B88" t="n">
+        <v>206.830857963</v>
+      </c>
+      <c r="C88" t="n">
+        <v>16314.24304972501</v>
+      </c>
+      <c r="D88" t="n">
+        <v>302.192200961</v>
+      </c>
+      <c r="E88" t="n">
+        <v>680.4145114139997</v>
+      </c>
+      <c r="F88" t="n">
         <v>13482.556802146</v>
       </c>
-      <c r="C88" t="n">
+      <c r="G88" t="n">
         <v>13197.795380227</v>
       </c>
-      <c r="D88" t="n">
-        <v>16314.24304972501</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="H88" t="n">
         <v>781.4015643390001</v>
       </c>
-      <c r="F88" t="n">
-        <v>851.8206804019999</v>
-      </c>
-      <c r="G88" t="n">
-        <v>680.4145114139997</v>
-      </c>
-      <c r="H88" t="n">
-        <v>105.526021169</v>
+      <c r="I88" t="n">
+        <v>1302.941852799</v>
       </c>
     </row>
     <row r="89">
@@ -3154,25 +3448,28 @@
         <v>44652</v>
       </c>
       <c r="B89" t="n">
+        <v>202.664837779</v>
+      </c>
+      <c r="C89" t="n">
+        <v>12632.948609494</v>
+      </c>
+      <c r="D89" t="n">
+        <v>258.4550501629999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>883.6370101419992</v>
+      </c>
+      <c r="F89" t="n">
         <v>12820.784976796</v>
       </c>
-      <c r="C89" t="n">
+      <c r="G89" t="n">
         <v>12747.591166469</v>
       </c>
-      <c r="D89" t="n">
-        <v>12632.948609494</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="H89" t="n">
         <v>642.5687365000001</v>
       </c>
-      <c r="F89" t="n">
-        <v>726.8006352279999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>883.6370101419992</v>
-      </c>
-      <c r="H89" t="n">
-        <v>64.15402147</v>
+      <c r="I89" t="n">
+        <v>1089.462934441</v>
       </c>
     </row>
     <row r="90">
@@ -3180,25 +3477,28 @@
         <v>44682</v>
       </c>
       <c r="B90" t="n">
+        <v>240.631118414</v>
+      </c>
+      <c r="C90" t="n">
+        <v>11816.951298538</v>
+      </c>
+      <c r="D90" t="n">
+        <v>243.521288973</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1001.368317252</v>
+      </c>
+      <c r="F90" t="n">
         <v>13067.921745451</v>
       </c>
-      <c r="C90" t="n">
+      <c r="G90" t="n">
         <v>13911.955782361</v>
       </c>
-      <c r="D90" t="n">
-        <v>11816.951298538</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="H90" t="n">
         <v>808.1733624789999</v>
       </c>
-      <c r="F90" t="n">
-        <v>776.9905043690001</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1001.368317252</v>
-      </c>
-      <c r="H90" t="n">
-        <v>28.957689508</v>
+      <c r="I90" t="n">
+        <v>969.8503823609999</v>
       </c>
     </row>
     <row r="91">
@@ -3206,25 +3506,28 @@
         <v>44713</v>
       </c>
       <c r="B91" t="n">
+        <v>275.5641808579998</v>
+      </c>
+      <c r="C91" t="n">
+        <v>12206.115883757</v>
+      </c>
+      <c r="D91" t="n">
+        <v>250.042843738</v>
+      </c>
+      <c r="E91" t="n">
+        <v>720.6986375800028</v>
+      </c>
+      <c r="F91" t="n">
         <v>14902.514387136</v>
       </c>
-      <c r="C91" t="n">
+      <c r="G91" t="n">
         <v>14013.536413405</v>
       </c>
-      <c r="D91" t="n">
-        <v>12206.115883757</v>
-      </c>
-      <c r="E91" t="n">
+      <c r="H91" t="n">
         <v>627.0363017519999</v>
       </c>
-      <c r="F91" t="n">
-        <v>801.2667899089997</v>
-      </c>
-      <c r="G91" t="n">
-        <v>720.6986375800028</v>
-      </c>
-      <c r="H91" t="n">
-        <v>51.127712958</v>
+      <c r="I91" t="n">
+        <v>980.8760608809998</v>
       </c>
     </row>
     <row r="92">
@@ -3232,25 +3535,28 @@
         <v>44743</v>
       </c>
       <c r="B92" t="n">
+        <v>393.3205400790001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>14475.051629303</v>
+      </c>
+      <c r="D92" t="n">
+        <v>135.2731059459999</v>
+      </c>
+      <c r="E92" t="n">
+        <v>744.3472838200017</v>
+      </c>
+      <c r="F92" t="n">
         <v>18773.191790112</v>
       </c>
-      <c r="C92" t="n">
+      <c r="G92" t="n">
         <v>14590.496589518</v>
       </c>
-      <c r="D92" t="n">
-        <v>14475.051629303</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="H92" t="n">
         <v>724.6476680730001</v>
       </c>
-      <c r="F92" t="n">
-        <v>814.599718471</v>
-      </c>
-      <c r="G92" t="n">
-        <v>744.3472838200017</v>
-      </c>
-      <c r="H92" t="n">
-        <v>71.40759651199998</v>
+      <c r="I92" t="n">
+        <v>1149.312951602</v>
       </c>
     </row>
     <row r="93">
@@ -3258,25 +3564,28 @@
         <v>44774</v>
       </c>
       <c r="B93" t="n">
+        <v>685.2887200700006</v>
+      </c>
+      <c r="C93" t="n">
+        <v>12906.32326417801</v>
+      </c>
+      <c r="D93" t="n">
+        <v>234.418125292</v>
+      </c>
+      <c r="E93" t="n">
+        <v>644.5862415949967</v>
+      </c>
+      <c r="F93" t="n">
         <v>18110.243995545</v>
       </c>
-      <c r="C93" t="n">
+      <c r="G93" t="n">
         <v>15487.039179734</v>
       </c>
-      <c r="D93" t="n">
-        <v>12906.32326417801</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="H93" t="n">
         <v>900.5189835330001</v>
       </c>
-      <c r="F93" t="n">
-        <v>1247.767880976001</v>
-      </c>
-      <c r="G93" t="n">
-        <v>644.5862415949967</v>
-      </c>
-      <c r="H93" t="n">
-        <v>33.635192934</v>
+      <c r="I93" t="n">
+        <v>1196.883529759</v>
       </c>
     </row>
     <row r="94">
@@ -3284,25 +3593,28 @@
         <v>44805</v>
       </c>
       <c r="B94" t="n">
+        <v>480.216917204</v>
+      </c>
+      <c r="C94" t="n">
+        <v>11033.690717285</v>
+      </c>
+      <c r="D94" t="n">
+        <v>226.018916986</v>
+      </c>
+      <c r="E94" t="n">
+        <v>699.1886712370015</v>
+      </c>
+      <c r="F94" t="n">
         <v>14924.08755527</v>
       </c>
-      <c r="C94" t="n">
+      <c r="G94" t="n">
         <v>13402.906342611</v>
       </c>
-      <c r="D94" t="n">
-        <v>11033.690717285</v>
-      </c>
-      <c r="E94" t="n">
+      <c r="H94" t="n">
         <v>799.0239685519998</v>
       </c>
-      <c r="F94" t="n">
-        <v>1021.463351489</v>
-      </c>
-      <c r="G94" t="n">
-        <v>699.1886712370015</v>
-      </c>
-      <c r="H94" t="n">
-        <v>43.604646862</v>
+      <c r="I94" t="n">
+        <v>1103.650301544</v>
       </c>
     </row>
     <row r="95">
@@ -3310,25 +3622,28 @@
         <v>44835</v>
       </c>
       <c r="B95" t="n">
+        <v>247.4916528360001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>11146.850138101</v>
+      </c>
+      <c r="D95" t="n">
+        <v>252.43523779</v>
+      </c>
+      <c r="E95" t="n">
+        <v>781.8489488450022</v>
+      </c>
+      <c r="F95" t="n">
         <v>13972.418655136</v>
       </c>
-      <c r="C95" t="n">
+      <c r="G95" t="n">
         <v>13682.52603386</v>
       </c>
-      <c r="D95" t="n">
-        <v>11146.850138101</v>
-      </c>
-      <c r="E95" t="n">
+      <c r="H95" t="n">
         <v>864.9979461730001</v>
       </c>
-      <c r="F95" t="n">
-        <v>822.9510377080001</v>
-      </c>
-      <c r="G95" t="n">
-        <v>781.8489488450022</v>
-      </c>
-      <c r="H95" t="n">
-        <v>56.072229108</v>
+      <c r="I95" t="n">
+        <v>1153.608849223</v>
       </c>
     </row>
     <row r="96">
@@ -3336,25 +3651,28 @@
         <v>44866</v>
       </c>
       <c r="B96" t="n">
+        <v>208.893767341</v>
+      </c>
+      <c r="C96" t="n">
+        <v>12366.68903746</v>
+      </c>
+      <c r="D96" t="n">
+        <v>254.3669396439999</v>
+      </c>
+      <c r="E96" t="n">
+        <v>589.072011049</v>
+      </c>
+      <c r="F96" t="n">
         <v>14455.059859818</v>
       </c>
-      <c r="C96" t="n">
+      <c r="G96" t="n">
         <v>13336.5436566</v>
       </c>
-      <c r="D96" t="n">
-        <v>12366.68903746</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="H96" t="n">
         <v>876.1655467060001</v>
       </c>
-      <c r="F96" t="n">
-        <v>774.908435781</v>
-      </c>
-      <c r="G96" t="n">
-        <v>589.072011049</v>
-      </c>
-      <c r="H96" t="n">
-        <v>67.59380478200001</v>
+      <c r="I96" t="n">
+        <v>997.886778779</v>
       </c>
     </row>
     <row r="97">
@@ -3362,25 +3680,28 @@
         <v>44896</v>
       </c>
       <c r="B97" t="n">
+        <v>194.697768681</v>
+      </c>
+      <c r="C97" t="n">
+        <v>16410.51309099499</v>
+      </c>
+      <c r="D97" t="n">
+        <v>448.26524511</v>
+      </c>
+      <c r="E97" t="n">
+        <v>444.8733583799994</v>
+      </c>
+      <c r="F97" t="n">
         <v>18145.157089543</v>
       </c>
-      <c r="C97" t="n">
+      <c r="G97" t="n">
         <v>14498.185915205</v>
       </c>
-      <c r="D97" t="n">
-        <v>16410.51309099499</v>
-      </c>
-      <c r="E97" t="n">
+      <c r="H97" t="n">
         <v>928.4124068000001</v>
       </c>
-      <c r="F97" t="n">
-        <v>955.3025921130002</v>
-      </c>
-      <c r="G97" t="n">
-        <v>444.8733583799994</v>
-      </c>
-      <c r="H97" t="n">
-        <v>102.990375852</v>
+      <c r="I97" t="n">
+        <v>1249.326334842</v>
       </c>
     </row>
     <row r="98">
@@ -3388,25 +3709,28 @@
         <v>44927</v>
       </c>
       <c r="B98" t="n">
+        <v>201.41865021</v>
+      </c>
+      <c r="C98" t="n">
+        <v>15038.850118819</v>
+      </c>
+      <c r="D98" t="n">
+        <v>418.606803641</v>
+      </c>
+      <c r="E98" t="n">
+        <v>593.4699590149999</v>
+      </c>
+      <c r="F98" t="n">
         <v>17320.821020977</v>
       </c>
-      <c r="C98" t="n">
+      <c r="G98" t="n">
         <v>14913.77644269</v>
       </c>
-      <c r="D98" t="n">
-        <v>15038.850118819</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="H98" t="n">
         <v>947.709163656</v>
       </c>
-      <c r="F98" t="n">
-        <v>932.998935777</v>
-      </c>
-      <c r="G98" t="n">
-        <v>593.4699590149999</v>
-      </c>
-      <c r="H98" t="n">
-        <v>128.583202482</v>
+      <c r="I98" t="n">
+        <v>1213.400072216</v>
       </c>
     </row>
     <row r="99">
@@ -3414,25 +3738,28 @@
         <v>44958</v>
       </c>
       <c r="B99" t="n">
+        <v>165.8693809230001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>13311.309414703</v>
+      </c>
+      <c r="D99" t="n">
+        <v>260.7615039790001</v>
+      </c>
+      <c r="E99" t="n">
+        <v>718.7154317130005</v>
+      </c>
+      <c r="F99" t="n">
         <v>15101.781741386</v>
       </c>
-      <c r="C99" t="n">
+      <c r="G99" t="n">
         <v>12961.934603267</v>
       </c>
-      <c r="D99" t="n">
-        <v>13311.309414703</v>
-      </c>
-      <c r="E99" t="n">
+      <c r="H99" t="n">
         <v>729.1587611520001</v>
       </c>
-      <c r="F99" t="n">
-        <v>685.6957911130003</v>
-      </c>
-      <c r="G99" t="n">
-        <v>718.7154317130005</v>
-      </c>
-      <c r="H99" t="n">
-        <v>98.53688128199998</v>
+      <c r="I99" t="n">
+        <v>1055.79775416</v>
       </c>
     </row>
     <row r="100">
@@ -3440,25 +3767,28 @@
         <v>44986</v>
       </c>
       <c r="B100" t="n">
+        <v>179.911709831</v>
+      </c>
+      <c r="C100" t="n">
+        <v>13777.9496322</v>
+      </c>
+      <c r="D100" t="n">
+        <v>286.4843145120001</v>
+      </c>
+      <c r="E100" t="n">
+        <v>956.5226185520004</v>
+      </c>
+      <c r="F100" t="n">
         <v>12309.22228106799</v>
       </c>
-      <c r="C100" t="n">
+      <c r="G100" t="n">
         <v>14467.718997713</v>
       </c>
-      <c r="D100" t="n">
-        <v>13777.9496322</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="H100" t="n">
         <v>850.1212037619998</v>
       </c>
-      <c r="F100" t="n">
-        <v>808.911183057</v>
-      </c>
-      <c r="G100" t="n">
-        <v>956.5226185520004</v>
-      </c>
-      <c r="H100" t="n">
-        <v>106.437872548</v>
+      <c r="I100" t="n">
+        <v>1249.541920517</v>
       </c>
     </row>
     <row r="101">
@@ -3466,25 +3796,28 @@
         <v>45017</v>
       </c>
       <c r="B101" t="n">
+        <v>189.5537022429999</v>
+      </c>
+      <c r="C101" t="n">
+        <v>11550.769862668</v>
+      </c>
+      <c r="D101" t="n">
+        <v>343.3634661070001</v>
+      </c>
+      <c r="E101" t="n">
+        <v>896.7287647789965</v>
+      </c>
+      <c r="F101" t="n">
         <v>12786.49740888</v>
       </c>
-      <c r="C101" t="n">
+      <c r="G101" t="n">
         <v>12905.762456797</v>
       </c>
-      <c r="D101" t="n">
-        <v>11550.769862668</v>
-      </c>
-      <c r="E101" t="n">
+      <c r="H101" t="n">
         <v>795.151848661</v>
       </c>
-      <c r="F101" t="n">
-        <v>890.567916382</v>
-      </c>
-      <c r="G101" t="n">
-        <v>896.7287647789965</v>
-      </c>
-      <c r="H101" t="n">
-        <v>57.867984216</v>
+      <c r="I101" t="n">
+        <v>1068.884664611</v>
       </c>
     </row>
     <row r="102">
@@ -3492,25 +3825,28 @@
         <v>45047</v>
       </c>
       <c r="B102" t="n">
+        <v>292.807897739</v>
+      </c>
+      <c r="C102" t="n">
+        <v>11431.881440773</v>
+      </c>
+      <c r="D102" t="n">
+        <v>240.129017757</v>
+      </c>
+      <c r="E102" t="n">
+        <v>957.3345176399955</v>
+      </c>
+      <c r="F102" t="n">
         <v>13243.68243296</v>
       </c>
-      <c r="C102" t="n">
+      <c r="G102" t="n">
         <v>13751.79503978</v>
       </c>
-      <c r="D102" t="n">
-        <v>11431.881440773</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="H102" t="n">
         <v>710.0675091520001</v>
       </c>
-      <c r="F102" t="n">
-        <v>898.065551204</v>
-      </c>
-      <c r="G102" t="n">
-        <v>957.3345176399955</v>
-      </c>
-      <c r="H102" t="n">
-        <v>49.600419554</v>
+      <c r="I102" t="n">
+        <v>1092.450924797</v>
       </c>
     </row>
     <row r="103">
@@ -3518,25 +3854,28 @@
         <v>45078</v>
       </c>
       <c r="B103" t="n">
+        <v>313.9032156900003</v>
+      </c>
+      <c r="C103" t="n">
+        <v>11686.182639186</v>
+      </c>
+      <c r="D103" t="n">
+        <v>190.093486269</v>
+      </c>
+      <c r="E103" t="n">
+        <v>963.3404787729974</v>
+      </c>
+      <c r="F103" t="n">
         <v>14796.250624565</v>
       </c>
-      <c r="C103" t="n">
+      <c r="G103" t="n">
         <v>13467.433389713</v>
       </c>
-      <c r="D103" t="n">
-        <v>11686.182639186</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="H103" t="n">
         <v>745.9609480900001</v>
       </c>
-      <c r="F103" t="n">
-        <v>781.0724426090005</v>
-      </c>
-      <c r="G103" t="n">
-        <v>963.3404787729974</v>
-      </c>
-      <c r="H103" t="n">
-        <v>35.078646778</v>
+      <c r="I103" t="n">
+        <v>978.0291497510002</v>
       </c>
     </row>
     <row r="104">
@@ -3544,25 +3883,28 @@
         <v>45108</v>
       </c>
       <c r="B104" t="n">
+        <v>671.921038704</v>
+      </c>
+      <c r="C104" t="n">
+        <v>13568.499928441</v>
+      </c>
+      <c r="D104" t="n">
+        <v>245.5081025560001</v>
+      </c>
+      <c r="E104" t="n">
+        <v>747.5305040660014</v>
+      </c>
+      <c r="F104" t="n">
         <v>17219.25976227899</v>
       </c>
-      <c r="C104" t="n">
+      <c r="G104" t="n">
         <v>15041.704805846</v>
       </c>
-      <c r="D104" t="n">
-        <v>13568.499928441</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="H104" t="n">
         <v>828.4823166470002</v>
       </c>
-      <c r="F104" t="n">
-        <v>1188.00966303</v>
-      </c>
-      <c r="G104" t="n">
-        <v>747.5305040660014</v>
-      </c>
-      <c r="H104" t="n">
-        <v>35.512120154</v>
+      <c r="I104" t="n">
+        <v>1147.500053721</v>
       </c>
     </row>
     <row r="105">
@@ -3570,25 +3912,28 @@
         <v>45139</v>
       </c>
       <c r="B105" t="n">
+        <v>417.1153602810001</v>
+      </c>
+      <c r="C105" t="n">
+        <v>14306.469246552</v>
+      </c>
+      <c r="D105" t="n">
+        <v>159.724331112</v>
+      </c>
+      <c r="E105" t="n">
+        <v>939.7301526730002</v>
+      </c>
+      <c r="F105" t="n">
         <v>18019.736191989</v>
       </c>
-      <c r="C105" t="n">
+      <c r="G105" t="n">
         <v>15084.17935216</v>
       </c>
-      <c r="D105" t="n">
-        <v>14306.469246552</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="H105" t="n">
         <v>875.1592506459998</v>
       </c>
-      <c r="F105" t="n">
-        <v>838.8752834620001</v>
-      </c>
-      <c r="G105" t="n">
-        <v>939.7301526730002</v>
-      </c>
-      <c r="H105" t="n">
-        <v>34.96925495</v>
+      <c r="I105" t="n">
+        <v>1242.542176375</v>
       </c>
     </row>
     <row r="106">
@@ -3596,25 +3941,28 @@
         <v>45170</v>
       </c>
       <c r="B106" t="n">
+        <v>448.4382490389999</v>
+      </c>
+      <c r="C106" t="n">
+        <v>12517.036803507</v>
+      </c>
+      <c r="D106" t="n">
+        <v>136.287665765</v>
+      </c>
+      <c r="E106" t="n">
+        <v>827.1712069630009</v>
+      </c>
+      <c r="F106" t="n">
         <v>14391.90829768</v>
       </c>
-      <c r="C106" t="n">
+      <c r="G106" t="n">
         <v>14242.800367821</v>
       </c>
-      <c r="D106" t="n">
-        <v>12517.036803507</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="H106" t="n">
         <v>863.5931066049997</v>
       </c>
-      <c r="F106" t="n">
-        <v>908.7144925439999</v>
-      </c>
-      <c r="G106" t="n">
-        <v>827.1712069630009</v>
-      </c>
-      <c r="H106" t="n">
-        <v>18.641397614</v>
+      <c r="I106" t="n">
+        <v>1156.921942641</v>
       </c>
     </row>
     <row r="107">
@@ -3622,25 +3970,28 @@
         <v>45200</v>
       </c>
       <c r="B107" t="n">
+        <v>280.5596002209999</v>
+      </c>
+      <c r="C107" t="n">
+        <v>10793.3268022</v>
+      </c>
+      <c r="D107" t="n">
+        <v>232.0385431210001</v>
+      </c>
+      <c r="E107" t="n">
+        <v>941.421234422997</v>
+      </c>
+      <c r="F107" t="n">
         <v>12676.829068939</v>
       </c>
-      <c r="C107" t="n">
+      <c r="G107" t="n">
         <v>14395.836385382</v>
       </c>
-      <c r="D107" t="n">
-        <v>10793.3268022</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="H107" t="n">
         <v>741.3013847269999</v>
       </c>
-      <c r="F107" t="n">
-        <v>889.5501517929999</v>
-      </c>
-      <c r="G107" t="n">
-        <v>941.421234422997</v>
-      </c>
-      <c r="H107" t="n">
-        <v>17.573294648</v>
+      <c r="I107" t="n">
+        <v>1225.074438663</v>
       </c>
     </row>
     <row r="108">
@@ -3648,25 +3999,28 @@
         <v>45231</v>
       </c>
       <c r="B108" t="n">
+        <v>224.868902696</v>
+      </c>
+      <c r="C108" t="n">
+        <v>11890.21919995099</v>
+      </c>
+      <c r="D108" t="n">
+        <v>455.885610787</v>
+      </c>
+      <c r="E108" t="n">
+        <v>669.3605158170006</v>
+      </c>
+      <c r="F108" t="n">
         <v>14097.67463097901</v>
       </c>
-      <c r="C108" t="n">
+      <c r="G108" t="n">
         <v>14823.448162432</v>
       </c>
-      <c r="D108" t="n">
-        <v>11890.21919995099</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="H108" t="n">
         <v>738.2904168199999</v>
       </c>
-      <c r="F108" t="n">
-        <v>1015.728088511</v>
-      </c>
-      <c r="G108" t="n">
-        <v>669.3605158170006</v>
-      </c>
-      <c r="H108" t="n">
-        <v>17.158527554</v>
+      <c r="I108" t="n">
+        <v>1321.93824342</v>
       </c>
     </row>
     <row r="109">
@@ -3674,25 +4028,28 @@
         <v>45261</v>
       </c>
       <c r="B109" t="n">
+        <v>274.3023144909998</v>
+      </c>
+      <c r="C109" t="n">
+        <v>13628.273495748</v>
+      </c>
+      <c r="D109" t="n">
+        <v>408.640031415</v>
+      </c>
+      <c r="E109" t="n">
+        <v>455.3355621590002</v>
+      </c>
+      <c r="F109" t="n">
         <v>16933.060743353</v>
       </c>
-      <c r="C109" t="n">
+      <c r="G109" t="n">
         <v>15493.754749067</v>
       </c>
-      <c r="D109" t="n">
-        <v>13628.273495748</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="H109" t="n">
         <v>870.027156754</v>
       </c>
-      <c r="F109" t="n">
-        <v>978.1900608479998</v>
-      </c>
-      <c r="G109" t="n">
-        <v>455.3355621590002</v>
-      </c>
-      <c r="H109" t="n">
-        <v>36.251636526</v>
+      <c r="I109" t="n">
+        <v>1382.412325883</v>
       </c>
     </row>
     <row r="110">
@@ -3700,25 +4057,28 @@
         <v>45292</v>
       </c>
       <c r="B110" t="n">
+        <v>215.6017699339999</v>
+      </c>
+      <c r="C110" t="n">
+        <v>15676.045087775</v>
+      </c>
+      <c r="D110" t="n">
+        <v>394.9408618439998</v>
+      </c>
+      <c r="E110" t="n">
+        <v>650.492602573999</v>
+      </c>
+      <c r="F110" t="n">
         <v>17363.13254006</v>
       </c>
-      <c r="C110" t="n">
+      <c r="G110" t="n">
         <v>14216.496849138</v>
       </c>
-      <c r="D110" t="n">
-        <v>15676.045087775</v>
-      </c>
-      <c r="E110" t="n">
+      <c r="H110" t="n">
         <v>825.0335520299997</v>
       </c>
-      <c r="F110" t="n">
-        <v>984.5977455309999</v>
-      </c>
-      <c r="G110" t="n">
-        <v>650.492602573999</v>
-      </c>
-      <c r="H110" t="n">
-        <v>24.189160562</v>
+      <c r="I110" t="n">
+        <v>1479.583969213</v>
       </c>
     </row>
     <row r="111">
@@ -3726,25 +4086,28 @@
         <v>45323</v>
       </c>
       <c r="B111" t="n">
+        <v>243.6418279780001</v>
+      </c>
+      <c r="C111" t="n">
+        <v>12781.62833038</v>
+      </c>
+      <c r="D111" t="n">
+        <v>286.3514712219998</v>
+      </c>
+      <c r="E111" t="n">
+        <v>572.7209215450022</v>
+      </c>
+      <c r="F111" t="n">
         <v>14104.359716382</v>
       </c>
-      <c r="C111" t="n">
+      <c r="G111" t="n">
         <v>13937.248314468</v>
       </c>
-      <c r="D111" t="n">
-        <v>12781.62833038</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="H111" t="n">
         <v>794.9487942109999</v>
       </c>
-      <c r="F111" t="n">
-        <v>880.1306995469999</v>
-      </c>
-      <c r="G111" t="n">
-        <v>572.7209215450022</v>
-      </c>
-      <c r="H111" t="n">
-        <v>12.763875054</v>
+      <c r="I111" t="n">
+        <v>1395.228239113</v>
       </c>
     </row>
     <row r="112">
@@ -3752,25 +4115,28 @@
         <v>45352</v>
       </c>
       <c r="B112" t="n">
+        <v>280.921168143</v>
+      </c>
+      <c r="C112" t="n">
+        <v>14385.308374664</v>
+      </c>
+      <c r="D112" t="n">
+        <v>386.2424436780001</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1018.705123363998</v>
+      </c>
+      <c r="F112" t="n">
         <v>12334.385936293</v>
       </c>
-      <c r="C112" t="n">
+      <c r="G112" t="n">
         <v>14690.784426296</v>
       </c>
-      <c r="D112" t="n">
-        <v>14385.308374664</v>
-      </c>
-      <c r="E112" t="n">
+      <c r="H112" t="n">
         <v>866.3973632499997</v>
       </c>
-      <c r="F112" t="n">
-        <v>1131.442173385</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1018.705123363998</v>
-      </c>
-      <c r="H112" t="n">
-        <v>13.053860666</v>
+      <c r="I112" t="n">
+        <v>1483.072722346</v>
       </c>
     </row>
     <row r="113">
@@ -3778,25 +4144,28 @@
         <v>45383</v>
       </c>
       <c r="B113" t="n">
+        <v>568.2538152950003</v>
+      </c>
+      <c r="C113" t="n">
+        <v>11626.500370414</v>
+      </c>
+      <c r="D113" t="n">
+        <v>204.3194088129999</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1027.388117136999</v>
+      </c>
+      <c r="F113" t="n">
         <v>10913.73920824699</v>
       </c>
-      <c r="C113" t="n">
+      <c r="G113" t="n">
         <v>13635.817819423</v>
       </c>
-      <c r="D113" t="n">
-        <v>11626.500370414</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="H113" t="n">
         <v>785.2096457409997</v>
       </c>
-      <c r="F113" t="n">
-        <v>1196.930697618</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1027.388117136999</v>
-      </c>
-      <c r="H113" t="n">
-        <v>5.76390269</v>
+      <c r="I113" t="n">
+        <v>1388.501837393</v>
       </c>
     </row>
     <row r="114">
@@ -3804,25 +4173,28 @@
         <v>45413</v>
       </c>
       <c r="B114" t="n">
+        <v>512.1260622529998</v>
+      </c>
+      <c r="C114" t="n">
+        <v>11968.988827786</v>
+      </c>
+      <c r="D114" t="n">
+        <v>313.510439124</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1321.803718287003</v>
+      </c>
+      <c r="F114" t="n">
         <v>9662.490970205996</v>
       </c>
-      <c r="C114" t="n">
+      <c r="G114" t="n">
         <v>15051.032256459</v>
       </c>
-      <c r="D114" t="n">
-        <v>11968.988827786</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="H114" t="n">
         <v>691.9980733900002</v>
       </c>
-      <c r="F114" t="n">
-        <v>1289.479212133</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1321.803718287003</v>
-      </c>
-      <c r="H114" t="n">
-        <v>4.334806</v>
+      <c r="I114" t="n">
+        <v>1423.99258729</v>
       </c>
     </row>
     <row r="115">
@@ -3830,25 +4202,28 @@
         <v>45444</v>
       </c>
       <c r="B115" t="n">
+        <v>465.677340816</v>
+      </c>
+      <c r="C115" t="n">
+        <v>12715.939037963</v>
+      </c>
+      <c r="D115" t="n">
+        <v>142.3154625939999</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1159.065319749</v>
+      </c>
+      <c r="F115" t="n">
         <v>12114.243989432</v>
       </c>
-      <c r="C115" t="n">
+      <c r="G115" t="n">
         <v>14321.424437653</v>
       </c>
-      <c r="D115" t="n">
-        <v>12715.939037963</v>
-      </c>
-      <c r="E115" t="n">
+      <c r="H115" t="n">
         <v>749.2726988720001</v>
       </c>
-      <c r="F115" t="n">
-        <v>955.632692525</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1159.065319749</v>
-      </c>
-      <c r="H115" t="n">
-        <v>3.640774452</v>
+      <c r="I115" t="n">
+        <v>1330.727186999</v>
       </c>
     </row>
     <row r="116">
@@ -3856,25 +4231,28 @@
         <v>45474</v>
       </c>
       <c r="B116" t="n">
+        <v>628.6281459760003</v>
+      </c>
+      <c r="C116" t="n">
+        <v>15002.789876596</v>
+      </c>
+      <c r="D116" t="n">
+        <v>329.949938542</v>
+      </c>
+      <c r="E116" t="n">
+        <v>890.3779296829965</v>
+      </c>
+      <c r="F116" t="n">
         <v>15513.28302090101</v>
       </c>
-      <c r="C116" t="n">
+      <c r="G116" t="n">
         <v>15665.953470542</v>
       </c>
-      <c r="D116" t="n">
-        <v>15002.789876596</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="H116" t="n">
         <v>879.5935857060002</v>
       </c>
-      <c r="F116" t="n">
-        <v>1302.678403855</v>
-      </c>
-      <c r="G116" t="n">
-        <v>890.3779296829965</v>
-      </c>
-      <c r="H116" t="n">
-        <v>5.66298474</v>
+      <c r="I116" t="n">
+        <v>1460.141912578</v>
       </c>
     </row>
     <row r="117">
@@ -3882,25 +4260,28 @@
         <v>45505</v>
       </c>
       <c r="B117" t="n">
+        <v>389.7726829130001</v>
+      </c>
+      <c r="C117" t="n">
+        <v>16690.897468321</v>
+      </c>
+      <c r="D117" t="n">
+        <v>124.425064891</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1173.412028725998</v>
+      </c>
+      <c r="F117" t="n">
         <v>18433.72076801199</v>
       </c>
-      <c r="C117" t="n">
+      <c r="G117" t="n">
         <v>14738.385707382</v>
       </c>
-      <c r="D117" t="n">
-        <v>16690.897468321</v>
-      </c>
-      <c r="E117" t="n">
+      <c r="H117" t="n">
         <v>1094.520269876</v>
       </c>
-      <c r="F117" t="n">
-        <v>885.3775250050001</v>
-      </c>
-      <c r="G117" t="n">
-        <v>1173.412028725998</v>
-      </c>
-      <c r="H117" t="n">
-        <v>16.132442424</v>
+      <c r="I117" t="n">
+        <v>1244.098130405</v>
       </c>
     </row>
     <row r="118">
@@ -3908,25 +4289,28 @@
         <v>45536</v>
       </c>
       <c r="B118" t="n">
+        <v>295.672154609</v>
+      </c>
+      <c r="C118" t="n">
+        <v>13512.178924228</v>
+      </c>
+      <c r="D118" t="n">
+        <v>139.462982062</v>
+      </c>
+      <c r="E118" t="n">
+        <v>977.1052426059999</v>
+      </c>
+      <c r="F118" t="n">
         <v>14464.00300182699</v>
       </c>
-      <c r="C118" t="n">
+      <c r="G118" t="n">
         <v>15055.454320307</v>
       </c>
-      <c r="D118" t="n">
-        <v>13512.178924228</v>
-      </c>
-      <c r="E118" t="n">
+      <c r="H118" t="n">
         <v>818.922765405</v>
       </c>
-      <c r="F118" t="n">
-        <v>787.093888844</v>
-      </c>
-      <c r="G118" t="n">
-        <v>977.1052426059999</v>
-      </c>
-      <c r="H118" t="n">
-        <v>6.248554395999999</v>
+      <c r="I118" t="n">
+        <v>1377.99842379</v>
       </c>
     </row>
     <row r="119">
@@ -3934,25 +4318,28 @@
         <v>45566</v>
       </c>
       <c r="B119" t="n">
+        <v>231.6747273179998</v>
+      </c>
+      <c r="C119" t="n">
+        <v>11842.847747533</v>
+      </c>
+      <c r="D119" t="n">
+        <v>217.3189620749999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>794.4744363660002</v>
+      </c>
+      <c r="F119" t="n">
         <v>11088.437256949</v>
       </c>
-      <c r="C119" t="n">
+      <c r="G119" t="n">
         <v>16211.570475249</v>
       </c>
-      <c r="D119" t="n">
-        <v>11842.847747533</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="H119" t="n">
         <v>811.8762850440002</v>
       </c>
-      <c r="F119" t="n">
-        <v>853.7212427009997</v>
-      </c>
-      <c r="G119" t="n">
-        <v>794.4744363660002</v>
-      </c>
-      <c r="H119" t="n">
-        <v>3.310888182</v>
+      <c r="I119" t="n">
+        <v>1429.20213142</v>
       </c>
     </row>
     <row r="120">
@@ -3960,25 +4347,28 @@
         <v>45597</v>
       </c>
       <c r="B120" t="n">
+        <v>198.701034147</v>
+      </c>
+      <c r="C120" t="n">
+        <v>12772.672410239</v>
+      </c>
+      <c r="D120" t="n">
+        <v>301.954425559</v>
+      </c>
+      <c r="E120" t="n">
+        <v>732.1395870100019</v>
+      </c>
+      <c r="F120" t="n">
         <v>11146.76999537201</v>
       </c>
-      <c r="C120" t="n">
+      <c r="G120" t="n">
         <v>15338.810197107</v>
       </c>
-      <c r="D120" t="n">
-        <v>12772.672410239</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="H120" t="n">
         <v>755.431186747</v>
       </c>
-      <c r="F120" t="n">
-        <v>873.077761305</v>
-      </c>
-      <c r="G120" t="n">
-        <v>732.1395870100019</v>
-      </c>
-      <c r="H120" t="n">
-        <v>3.897590256</v>
+      <c r="I120" t="n">
+        <v>1383.967937649</v>
       </c>
     </row>
     <row r="121">
@@ -3986,25 +4376,28 @@
         <v>45627</v>
       </c>
       <c r="B121" t="n">
+        <v>209.4713384029999</v>
+      </c>
+      <c r="C121" t="n">
+        <v>14754.645191133</v>
+      </c>
+      <c r="D121" t="n">
+        <v>514.8516964390002</v>
+      </c>
+      <c r="E121" t="n">
+        <v>698.3598124280018</v>
+      </c>
+      <c r="F121" t="n">
         <v>14248.10891039</v>
       </c>
-      <c r="C121" t="n">
+      <c r="G121" t="n">
         <v>15886.486225804</v>
       </c>
-      <c r="D121" t="n">
-        <v>14754.645191133</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="H121" t="n">
         <v>856.071259521</v>
       </c>
-      <c r="F121" t="n">
-        <v>1125.289538654</v>
-      </c>
-      <c r="G121" t="n">
-        <v>698.3598124280018</v>
-      </c>
-      <c r="H121" t="n">
-        <v>16.806253618</v>
+      <c r="I121" t="n">
+        <v>1582.977228664</v>
       </c>
     </row>
     <row r="122">
@@ -4012,25 +4405,28 @@
         <v>45658</v>
       </c>
       <c r="B122" t="n">
+        <v>219.540678122</v>
+      </c>
+      <c r="C122" t="n">
+        <v>15345.159353566</v>
+      </c>
+      <c r="D122" t="n">
+        <v>403.416248987</v>
+      </c>
+      <c r="E122" t="n">
+        <v>722.9967098850012</v>
+      </c>
+      <c r="F122" t="n">
         <v>12708.756423268</v>
       </c>
-      <c r="C122" t="n">
+      <c r="G122" t="n">
         <v>17014.959882135</v>
       </c>
-      <c r="D122" t="n">
-        <v>15345.159353566</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="H122" t="n">
         <v>1034.56221193</v>
       </c>
-      <c r="F122" t="n">
-        <v>1040.122015166</v>
-      </c>
-      <c r="G122" t="n">
-        <v>722.9967098850012</v>
-      </c>
-      <c r="H122" t="n">
-        <v>28.102065404</v>
+      <c r="I122" t="n">
+        <v>1394.599660855</v>
       </c>
     </row>
     <row r="123">
@@ -4038,25 +4434,28 @@
         <v>45689</v>
       </c>
       <c r="B123" t="n">
+        <v>188.9775192770001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>14953.785690567</v>
+      </c>
+      <c r="D123" t="n">
+        <v>483.295455587</v>
+      </c>
+      <c r="E123" t="n">
+        <v>934.9140457769985</v>
+      </c>
+      <c r="F123" t="n">
         <v>10949.939759308</v>
       </c>
-      <c r="C123" t="n">
+      <c r="G123" t="n">
         <v>15429.97763795</v>
       </c>
-      <c r="D123" t="n">
-        <v>14953.785690567</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="H123" t="n">
         <v>964.2315146550002</v>
       </c>
-      <c r="F123" t="n">
-        <v>1044.08292093</v>
-      </c>
-      <c r="G123" t="n">
-        <v>934.9140457769985</v>
-      </c>
-      <c r="H123" t="n">
-        <v>17.75190263</v>
+      <c r="I123" t="n">
+        <v>1288.818586449</v>
       </c>
     </row>
     <row r="124">
@@ -4064,25 +4463,28 @@
         <v>45717</v>
       </c>
       <c r="B124" t="n">
+        <v>197.594850767</v>
+      </c>
+      <c r="C124" t="n">
+        <v>14627.13324611799</v>
+      </c>
+      <c r="D124" t="n">
+        <v>343.432977151</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1106.354730649999</v>
+      </c>
+      <c r="F124" t="n">
         <v>9163.176841588003</v>
       </c>
-      <c r="C124" t="n">
+      <c r="G124" t="n">
         <v>16997.188756116</v>
       </c>
-      <c r="D124" t="n">
-        <v>14627.13324611799</v>
-      </c>
-      <c r="E124" t="n">
+      <c r="H124" t="n">
         <v>957.754578002</v>
       </c>
-      <c r="F124" t="n">
-        <v>984.7312513629998</v>
-      </c>
-      <c r="G124" t="n">
-        <v>1106.354730649999</v>
-      </c>
-      <c r="H124" t="n">
-        <v>5.2303167</v>
+      <c r="I124" t="n">
+        <v>1292.156566695</v>
       </c>
     </row>
     <row r="125">
@@ -4090,25 +4492,28 @@
         <v>45748</v>
       </c>
       <c r="B125" t="n">
+        <v>242.4548521800001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>13197.766604438</v>
+      </c>
+      <c r="D125" t="n">
+        <v>313.135767283</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1323.936099573001</v>
+      </c>
+      <c r="F125" t="n">
         <v>7936.025996147999</v>
       </c>
-      <c r="C125" t="n">
+      <c r="G125" t="n">
         <v>15163.555258153</v>
       </c>
-      <c r="D125" t="n">
-        <v>13197.766604438</v>
-      </c>
-      <c r="E125" t="n">
+      <c r="H125" t="n">
         <v>912.8810136010001</v>
       </c>
-      <c r="F125" t="n">
-        <v>982.2116827680002</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1323.936099573001</v>
-      </c>
-      <c r="H125" t="n">
-        <v>3.97790295</v>
+      <c r="I125" t="n">
+        <v>1301.804215305</v>
       </c>
     </row>
     <row r="126">
@@ -4116,25 +4521,28 @@
         <v>45778</v>
       </c>
       <c r="B126" t="n">
+        <v>426.2614820929999</v>
+      </c>
+      <c r="C126" t="n">
+        <v>11770.904122927</v>
+      </c>
+      <c r="D126" t="n">
+        <v>282.381733106</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1193.869244265002</v>
+      </c>
+      <c r="F126" t="n">
         <v>10199.133736353</v>
       </c>
-      <c r="C126" t="n">
+      <c r="G126" t="n">
         <v>15112.346853295</v>
       </c>
-      <c r="D126" t="n">
-        <v>11770.904122927</v>
-      </c>
-      <c r="E126" t="n">
+      <c r="H126" t="n">
         <v>1028.939049287</v>
       </c>
-      <c r="F126" t="n">
-        <v>1129.79438945</v>
-      </c>
-      <c r="G126" t="n">
-        <v>1193.869244265002</v>
-      </c>
-      <c r="H126" t="n">
-        <v>3.5838159</v>
+      <c r="I126" t="n">
+        <v>1256.785484072</v>
       </c>
     </row>
     <row r="127">
@@ -4142,25 +4550,28 @@
         <v>45809</v>
       </c>
       <c r="B127" t="n">
+        <v>433.871103771</v>
+      </c>
+      <c r="C127" t="n">
+        <v>11428.94545113499</v>
+      </c>
+      <c r="D127" t="n">
+        <v>215.931867354</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1226.919123745</v>
+      </c>
+      <c r="F127" t="n">
         <v>13360.796790048</v>
       </c>
-      <c r="C127" t="n">
+      <c r="G127" t="n">
         <v>14318.384971371</v>
       </c>
-      <c r="D127" t="n">
-        <v>11428.94545113499</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="H127" t="n">
         <v>871.0731347789999</v>
       </c>
-      <c r="F127" t="n">
-        <v>994.774412153</v>
-      </c>
-      <c r="G127" t="n">
-        <v>1226.919123745</v>
-      </c>
-      <c r="H127" t="n">
-        <v>3.327556344</v>
+      <c r="I127" t="n">
+        <v>1372.478859638</v>
       </c>
     </row>
     <row r="128">
@@ -4168,25 +4579,28 @@
         <v>45839</v>
       </c>
       <c r="B128" t="n">
+        <v>289.069793386</v>
+      </c>
+      <c r="C128" t="n">
+        <v>13719.732639278</v>
+      </c>
+      <c r="D128" t="n">
+        <v>202.047148482</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1339.564331233992</v>
+      </c>
+      <c r="F128" t="n">
         <v>19582.285691544</v>
       </c>
-      <c r="C128" t="n">
+      <c r="G128" t="n">
         <v>14486.528785949</v>
       </c>
-      <c r="D128" t="n">
-        <v>13719.732639278</v>
-      </c>
-      <c r="E128" t="n">
+      <c r="H128" t="n">
         <v>968.7359634080001</v>
       </c>
-      <c r="F128" t="n">
-        <v>838.001141543</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1339.564331233992</v>
-      </c>
-      <c r="H128" t="n">
-        <v>5.743067862</v>
+      <c r="I128" t="n">
+        <v>1526.307425242</v>
       </c>
     </row>
     <row r="129">
@@ -4194,25 +4608,28 @@
         <v>45870</v>
       </c>
       <c r="B129" t="n">
+        <v>306.2502717899998</v>
+      </c>
+      <c r="C129" t="n">
+        <v>14852.734065107</v>
+      </c>
+      <c r="D129" t="n">
+        <v>162.6897919129999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1230.062577705992</v>
+      </c>
+      <c r="F129" t="n">
         <v>20208.165090741</v>
       </c>
-      <c r="C129" t="n">
+      <c r="G129" t="n">
         <v>13354.21258711</v>
       </c>
-      <c r="D129" t="n">
-        <v>14852.734065107</v>
-      </c>
-      <c r="E129" t="n">
+      <c r="H129" t="n">
         <v>1090.544804585</v>
       </c>
-      <c r="F129" t="n">
-        <v>765.5717945269996</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1230.062577705992</v>
-      </c>
-      <c r="H129" t="n">
-        <v>9.065450772</v>
+      <c r="I129" t="n">
+        <v>1193.392404439</v>
       </c>
     </row>
     <row r="130">
@@ -4220,25 +4637,28 @@
         <v>45901</v>
       </c>
       <c r="B130" t="n">
+        <v>396.4064692020002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>11376.769638684</v>
+      </c>
+      <c r="D130" t="n">
+        <v>184.7827541850001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>894.8127407900013</v>
+      </c>
+      <c r="F130" t="n">
         <v>18203.05823853901</v>
       </c>
-      <c r="C130" t="n">
+      <c r="G130" t="n">
         <v>13520.598882845</v>
       </c>
-      <c r="D130" t="n">
-        <v>11376.769638684</v>
-      </c>
-      <c r="E130" t="n">
+      <c r="H130" t="n">
         <v>891.2656250810001</v>
       </c>
-      <c r="F130" t="n">
-        <v>875.5967540920004</v>
-      </c>
-      <c r="G130" t="n">
-        <v>894.8127407900013</v>
-      </c>
-      <c r="H130" t="n">
-        <v>51.69695328</v>
+      <c r="I130" t="n">
+        <v>1194.478416926</v>
       </c>
     </row>
     <row r="131">
@@ -4246,25 +4666,28 @@
         <v>45931</v>
       </c>
       <c r="B131" t="n">
+        <v>570.865706658</v>
+      </c>
+      <c r="C131" t="n">
+        <v>11850.168757536</v>
+      </c>
+      <c r="D131" t="n">
+        <v>217.680192491</v>
+      </c>
+      <c r="E131" t="n">
+        <v>827.5661459120021</v>
+      </c>
+      <c r="F131" t="n">
         <v>12913.024435929</v>
       </c>
-      <c r="C131" t="n">
+      <c r="G131" t="n">
         <v>13047.232004723</v>
       </c>
-      <c r="D131" t="n">
-        <v>11850.168757536</v>
-      </c>
-      <c r="E131" t="n">
+      <c r="H131" t="n">
         <v>914.5593871730003</v>
       </c>
-      <c r="F131" t="n">
-        <v>1136.952297416</v>
-      </c>
-      <c r="G131" t="n">
-        <v>827.5661459120021</v>
-      </c>
-      <c r="H131" t="n">
-        <v>3.88764558</v>
+      <c r="I131" t="n">
+        <v>1398.456840902</v>
       </c>
     </row>
     <row r="132">
@@ -4272,25 +4695,28 @@
         <v>45962</v>
       </c>
       <c r="B132" t="n">
+        <v>264.546668166</v>
+      </c>
+      <c r="C132" t="n">
+        <v>12843.00490621601</v>
+      </c>
+      <c r="D132" t="n">
+        <v>355.4071585660001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>926.0725661180003</v>
+      </c>
+      <c r="F132" t="n">
         <v>12906.205140017</v>
       </c>
-      <c r="C132" t="n">
+      <c r="G132" t="n">
         <v>12403.744685544</v>
       </c>
-      <c r="D132" t="n">
-        <v>12843.00490621601</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="H132" t="n">
         <v>988.028819824</v>
       </c>
-      <c r="F132" t="n">
-        <v>990.4139160390001</v>
-      </c>
-      <c r="G132" t="n">
-        <v>926.0725661180003</v>
-      </c>
-      <c r="H132" t="n">
-        <v>3.80598246</v>
+      <c r="I132" t="n">
+        <v>1410.24686981</v>
       </c>
     </row>
     <row r="133">
@@ -4298,25 +4724,28 @@
         <v>45992</v>
       </c>
       <c r="B133" t="n">
+        <v>219.2596976669999</v>
+      </c>
+      <c r="C133" t="n">
+        <v>13261.21008368501</v>
+      </c>
+      <c r="D133" t="n">
+        <v>469.603321541</v>
+      </c>
+      <c r="E133" t="n">
+        <v>762.8642622819992</v>
+      </c>
+      <c r="F133" t="n">
         <v>16659.882935206</v>
       </c>
-      <c r="C133" t="n">
+      <c r="G133" t="n">
         <v>14700.743303803</v>
       </c>
-      <c r="D133" t="n">
-        <v>13261.21008368501</v>
-      </c>
-      <c r="E133" t="n">
+      <c r="H133" t="n">
         <v>1109.615242019</v>
       </c>
-      <c r="F133" t="n">
-        <v>1022.588513104</v>
-      </c>
-      <c r="G133" t="n">
-        <v>762.8642622819992</v>
-      </c>
-      <c r="H133" t="n">
-        <v>23.703780898</v>
+      <c r="I133" t="n">
+        <v>1311.015671643</v>
       </c>
     </row>
     <row r="134">
@@ -4324,25 +4753,28 @@
         <v>46023</v>
       </c>
       <c r="B134" t="n">
+        <v>213.1290723079998</v>
+      </c>
+      <c r="C134" t="n">
+        <v>16895.94036909399</v>
+      </c>
+      <c r="D134" t="n">
+        <v>586.0984227539998</v>
+      </c>
+      <c r="E134" t="n">
+        <v>919.6141834430006</v>
+      </c>
+      <c r="F134" t="n">
         <v>16247.89548522</v>
       </c>
-      <c r="C134" t="n">
+      <c r="G134" t="n">
         <v>13906.390604959</v>
       </c>
-      <c r="D134" t="n">
-        <v>16895.94036909399</v>
-      </c>
-      <c r="E134" t="n">
+      <c r="H134" t="n">
         <v>1049.801906811</v>
       </c>
-      <c r="F134" t="n">
-        <v>1089.291927762999</v>
-      </c>
-      <c r="G134" t="n">
-        <v>919.6141834430006</v>
-      </c>
-      <c r="H134" t="n">
-        <v>8.495461058</v>
+      <c r="I134" t="n">
+        <v>1253.472854995</v>
       </c>
     </row>
     <row r="135">
@@ -4350,25 +4782,28 @@
         <v>46054</v>
       </c>
       <c r="B135" t="n">
+        <v>192.388611119</v>
+      </c>
+      <c r="C135" t="n">
+        <v>13873.457896163</v>
+      </c>
+      <c r="D135" t="n">
+        <v>394.781678309</v>
+      </c>
+      <c r="E135" t="n">
+        <v>973.1175134960027</v>
+      </c>
+      <c r="F135" t="n">
         <v>13230.138236341</v>
       </c>
-      <c r="C135" t="n">
+      <c r="G135" t="n">
         <v>11465.521051459</v>
       </c>
-      <c r="D135" t="n">
-        <v>13873.457896163</v>
-      </c>
-      <c r="E135" t="n">
+      <c r="H135" t="n">
         <v>926.9590917430002</v>
       </c>
-      <c r="F135" t="n">
-        <v>845.9119645619999</v>
-      </c>
-      <c r="G135" t="n">
-        <v>973.1175134960027</v>
-      </c>
-      <c r="H135" t="n">
-        <v>5.760099996</v>
+      <c r="I135" t="n">
+        <v>1103.053357045</v>
       </c>
     </row>
     <row r="136">
@@ -4376,25 +4811,28 @@
         <v>46082</v>
       </c>
       <c r="B136" t="n">
+        <v>195.1245536880001</v>
+      </c>
+      <c r="C136" t="n">
+        <v>15028.63750801</v>
+      </c>
+      <c r="D136" t="n">
+        <v>223.049665613</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1281.459051186005</v>
+      </c>
+      <c r="F136" t="n">
         <v>12081.140584774</v>
       </c>
-      <c r="C136" t="n">
+      <c r="G136" t="n">
         <v>12594.541738514</v>
       </c>
-      <c r="D136" t="n">
-        <v>15028.63750801</v>
-      </c>
-      <c r="E136" t="n">
+      <c r="H136" t="n">
         <v>913.0565978039999</v>
       </c>
-      <c r="F136" t="n">
-        <v>706.6102916200001</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1281.459051186005</v>
-      </c>
-      <c r="H136" t="n">
-        <v>5.492301444</v>
+      <c r="I136" t="n">
+        <v>1209.782021708</v>
       </c>
     </row>
     <row r="137">
@@ -4402,25 +4840,28 @@
         <v>46113</v>
       </c>
       <c r="B137" t="n">
+        <v>238.8753170399997</v>
+      </c>
+      <c r="C137" t="n">
+        <v>12366.146266213</v>
+      </c>
+      <c r="D137" t="n">
+        <v>277.367805536</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1284.346940701007</v>
+      </c>
+      <c r="F137" t="n">
         <v>10800.243291869</v>
       </c>
-      <c r="C137" t="n">
+      <c r="G137" t="n">
         <v>12926.558730015</v>
       </c>
-      <c r="D137" t="n">
-        <v>12366.146266213</v>
-      </c>
-      <c r="E137" t="n">
+      <c r="H137" t="n">
         <v>869.3284457939999</v>
       </c>
-      <c r="F137" t="n">
-        <v>791.1863070469997</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1284.346940701007</v>
-      </c>
-      <c r="H137" t="n">
-        <v>3.800414142</v>
+      <c r="I137" t="n">
+        <v>1176.644120446</v>
       </c>
     </row>
     <row r="138">
@@ -4428,25 +4869,28 @@
         <v>46143</v>
       </c>
       <c r="B138" t="n">
+        <v>298.5185524840001</v>
+      </c>
+      <c r="C138" t="n">
+        <v>11542.878149869</v>
+      </c>
+      <c r="D138" t="n">
+        <v>257.558752338</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1470.703313283008</v>
+      </c>
+      <c r="F138" t="n">
         <v>11528.785425543</v>
       </c>
-      <c r="C138" t="n">
+      <c r="G138" t="n">
         <v>13513.12316704</v>
       </c>
-      <c r="D138" t="n">
-        <v>11542.878149869</v>
-      </c>
-      <c r="E138" t="n">
+      <c r="H138" t="n">
         <v>906.1260754920002</v>
       </c>
-      <c r="F138" t="n">
-        <v>896.5914699060002</v>
-      </c>
-      <c r="G138" t="n">
-        <v>1470.703313283008</v>
-      </c>
-      <c r="H138" t="n">
-        <v>3.3850201</v>
+      <c r="I138" t="n">
+        <v>1275.985085368</v>
       </c>
     </row>
     <row r="139">
@@ -4454,25 +4898,28 @@
         <v>46174</v>
       </c>
       <c r="B139" t="n">
+        <v>316.425359135</v>
+      </c>
+      <c r="C139" t="n">
+        <v>10804.380127497</v>
+      </c>
+      <c r="D139" t="n">
+        <v>156.404192547</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1398.278412269</v>
+      </c>
+      <c r="F139" t="n">
         <v>14687.503992105</v>
       </c>
-      <c r="C139" t="n">
+      <c r="G139" t="n">
         <v>13530.828373063</v>
       </c>
-      <c r="D139" t="n">
-        <v>10804.380127497</v>
-      </c>
-      <c r="E139" t="n">
+      <c r="H139" t="n">
         <v>823.8837070810001</v>
       </c>
-      <c r="F139" t="n">
-        <v>756.7672729660001</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1398.278412269</v>
-      </c>
-      <c r="H139" t="n">
-        <v>3.319940428</v>
+      <c r="I139" t="n">
+        <v>1163.681073349</v>
       </c>
     </row>
     <row r="140">
@@ -4480,25 +4927,28 @@
         <v>46204</v>
       </c>
       <c r="B140" t="n">
+        <v>369.6669683270002</v>
+      </c>
+      <c r="C140" t="n">
+        <v>12717.092014475</v>
+      </c>
+      <c r="D140" t="n">
+        <v>295.590819053</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1193.949001689002</v>
+      </c>
+      <c r="F140" t="n">
         <v>20211.22902104699</v>
       </c>
-      <c r="C140" t="n">
+      <c r="G140" t="n">
         <v>14648.740137417</v>
       </c>
-      <c r="D140" t="n">
-        <v>12717.092014475</v>
-      </c>
-      <c r="E140" t="n">
+      <c r="H140" t="n">
         <v>967.5715241589996</v>
       </c>
-      <c r="F140" t="n">
-        <v>919.6156151990002</v>
-      </c>
-      <c r="G140" t="n">
-        <v>1193.949001689002</v>
-      </c>
-      <c r="H140" t="n">
-        <v>3.762345678</v>
+      <c r="I140" t="n">
+        <v>1183.900609884</v>
       </c>
     </row>
     <row r="141">
@@ -4506,25 +4956,28 @@
         <v>46235</v>
       </c>
       <c r="B141" t="n">
+        <v>266.4209132969999</v>
+      </c>
+      <c r="C141" t="n">
+        <v>12256.238976657</v>
+      </c>
+      <c r="D141" t="n">
+        <v>164.423117352</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1258.284827538001</v>
+      </c>
+      <c r="F141" t="n">
         <v>20965.565517073</v>
       </c>
-      <c r="C141" t="n">
+      <c r="G141" t="n">
         <v>15094.996708081</v>
       </c>
-      <c r="D141" t="n">
-        <v>12256.238976657</v>
-      </c>
-      <c r="E141" t="n">
+      <c r="H141" t="n">
         <v>1054.96470007</v>
       </c>
-      <c r="F141" t="n">
-        <v>658.2587753639999</v>
-      </c>
-      <c r="G141" t="n">
-        <v>1258.284827538001</v>
-      </c>
-      <c r="H141" t="n">
-        <v>3.53853619</v>
+      <c r="I141" t="n">
+        <v>1157.523022303</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>South Korea power generation by fuel (KPX EPSIS, market + PPA) (to Aug/26)</a:t>
+              <a:t>South Korea power generation by fuel (KPX EPSIS, KPX power market) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -815,7 +815,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data: GWh per month of electricity traded through the KPX electricity market and PPAs, by fuel (EPSIS menu 'Electricity trading volume (power market and PPA)', all regions). Months are dated the 1st. Total_GWh = market + PPA total; Coal_GWh = bituminous + anthracite; Renewables_Total_GWh = fuel cell + IGCC + solar + wind + hydro + ocean + bio + waste (the grid-connected renewable plants that trade on the market; small behind-the-meter systems and self-generation are not in it). Pumped_Storage_GWh is the output of pumped-storage plants.</t>
+          <t>Data: GWh per month of electricity traded through the KPX electricity market, by fuel (EPSIS menu 'Electricity trading volume (power market and PPA)', all regions). Months are dated the 1st. Market_Total_GWh is the sum of the fuel columns. PPA_Total_GWh is the volume traded under PPAs, which the source does not split by fuel (reported Jan 2020 - Jun 2026, about 2.5 TWh a month; blank elsewhere); Total_GWh = market + PPA (equal to the market where the PPA is blank). Coal_GWh = bituminous + anthracite; Renewables_Total_GWh = fuel cell + IGCC + solar + wind + hydro + ocean + bio + waste (the grid-connected renewable plants that trade on the market; small behind-the-meter systems and self-generation are not in it). Pumped_Storage_GWh is the output of pumped-storage plants.</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/south_korea_power_generation_monthly.xlsx
@@ -23622,8 +23622,11 @@
       <c r="S296" t="n">
         <v>51587.74002853101</v>
       </c>
+      <c r="T296" t="n">
+        <v>2646.653</v>
+      </c>
       <c r="U296" t="n">
-        <v>51587.74002853101</v>
+        <v>54234.39302853101</v>
       </c>
     </row>
     <row r="297">
@@ -23684,8 +23687,11 @@
       <c r="S297" t="n">
         <v>52218.41778047998</v>
       </c>
+      <c r="T297" t="n">
+        <v>2694.485</v>
+      </c>
       <c r="U297" t="n">
-        <v>52218.41778047998</v>
+        <v>54912.90278047998</v>
       </c>
     </row>
   </sheetData>
